--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -15594,7 +15594,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>106.00</t>
+          <t>103.00</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>58.00</t>
+          <t>57.00</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>9677.50</t>
+          <t>9675.50</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>572.10</t>
+          <t>499.60</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>391.00</t>
+          <t>389.00</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>966.00</t>
+          <t>916.00</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C1604" t="inlineStr">
@@ -35790,7 +35790,7 @@
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C1608" t="inlineStr">
@@ -37792,7 +37792,7 @@
       </c>
       <c r="B1699" t="inlineStr">
         <is>
-          <t>192.00</t>
+          <t>191.00</t>
         </is>
       </c>
       <c r="C1699" t="inlineStr">
@@ -42874,7 +42874,7 @@
       </c>
       <c r="B1930" t="inlineStr">
         <is>
-          <t>1130.00</t>
+          <t>1129.00</t>
         </is>
       </c>
       <c r="C1930" t="inlineStr">
@@ -43116,7 +43116,7 @@
       </c>
       <c r="B1941" t="inlineStr">
         <is>
-          <t>837.00</t>
+          <t>787.00</t>
         </is>
       </c>
       <c r="C1941" t="inlineStr">
@@ -45448,7 +45448,7 @@
       </c>
       <c r="B2047" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C2047" t="inlineStr">
@@ -46900,7 +46900,7 @@
       </c>
       <c r="B2113" t="inlineStr">
         <is>
-          <t>906.00</t>
+          <t>905.00</t>
         </is>
       </c>
       <c r="C2113" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>166.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>296.00</t>
+          <t>294.00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>189.00</t>
+          <t>181.00</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>240.00</t>
+          <t>234.00</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>53.00</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>46.00</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>619.00</t>
+          <t>571.00</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -21314,7 +21314,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>805.00</t>
+          <t>804.00</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>9674.50</t>
+          <t>9671.50</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
@@ -24262,7 +24262,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>570.00</t>
+          <t>569.00</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="B1184" t="inlineStr">
         <is>
-          <t>338.00</t>
+          <t>336.00</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="C1611" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>130.00</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
@@ -40784,7 +40784,7 @@
       </c>
       <c r="B1835" t="inlineStr">
         <is>
-          <t>276.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="C1835" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>1225.00</t>
+          <t>1223.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>2440.00</t>
+          <t>2439.00</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -5034,7 +5034,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>527.14</t>
+          <t>500.14</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>803.00</t>
+          <t>801.00</t>
         </is>
       </c>
       <c r="C952" t="inlineStr">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>9666.50</t>
+          <t>9662.50</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>152.00</t>
+          <t>120.00</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
@@ -33986,7 +33986,7 @@
       </c>
       <c r="B1526" t="inlineStr">
         <is>
-          <t>558.00</t>
+          <t>486.00</t>
         </is>
       </c>
       <c r="C1526" t="inlineStr">
@@ -34162,7 +34162,7 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>209.00</t>
+          <t>199.00</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
@@ -35878,7 +35878,7 @@
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C1612" t="inlineStr">
@@ -42434,7 +42434,7 @@
       </c>
       <c r="B1910" t="inlineStr">
         <is>
-          <t>3648.00</t>
+          <t>3640.00</t>
         </is>
       </c>
       <c r="C1910" t="inlineStr">
@@ -42808,7 +42808,7 @@
       </c>
       <c r="B1927" t="inlineStr">
         <is>
-          <t>232.00</t>
+          <t>222.00</t>
         </is>
       </c>
       <c r="C1927" t="inlineStr">
@@ -45492,7 +45492,7 @@
       </c>
       <c r="B2049" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C2049" t="inlineStr">
@@ -45624,7 +45624,7 @@
       </c>
       <c r="B2055" t="inlineStr">
         <is>
-          <t>233.00</t>
+          <t>223.00</t>
         </is>
       </c>
       <c r="C2055" t="inlineStr">
@@ -45646,7 +45646,7 @@
       </c>
       <c r="B2056" t="inlineStr">
         <is>
-          <t>129.00</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="C2056" t="inlineStr">
@@ -46988,7 +46988,7 @@
       </c>
       <c r="B2117" t="inlineStr">
         <is>
-          <t>905.00</t>
+          <t>897.00</t>
         </is>
       </c>
       <c r="C2117" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>1354.00</t>
+          <t>1353.00</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -22238,7 +22238,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1591.00</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>584.00</t>
+          <t>580.00</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="B1823" t="inlineStr">
         <is>
-          <t>353.00</t>
+          <t>253.00</t>
         </is>
       </c>
       <c r="C1823" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="B2052" t="inlineStr">
         <is>
-          <t>216.00</t>
+          <t>212.00</t>
         </is>
       </c>
       <c r="C2052" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>91.00</t>
+          <t>89.00</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>3004.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>2986.00</t>
+          <t>2948.00</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -21006,17 +21006,17 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>2951.00</t>
+          <t>3500.00</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25296,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>4508.00</t>
+          <t>4498.00</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>289.00</t>
+          <t>214.00</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
@@ -28618,7 +28618,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>377.00</t>
+          <t>347.00</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr">
@@ -44348,7 +44348,7 @@
       </c>
       <c r="B1997" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>232.00</t>
         </is>
       </c>
       <c r="C1997" t="inlineStr">
@@ -44358,7 +44358,7 @@
       </c>
       <c r="D1997" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>530</t>
         </is>
       </c>
     </row>
@@ -45118,12 +45118,12 @@
       </c>
       <c r="B2032" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>967.00</t>
         </is>
       </c>
       <c r="C2032" t="inlineStr">
         <is>
-          <t>105.00</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="D2032" t="inlineStr">
@@ -47406,12 +47406,12 @@
       </c>
       <c r="B2136" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="C2136" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>1900.00</t>
         </is>
       </c>
       <c r="D2136" t="inlineStr">
@@ -47472,7 +47472,7 @@
       </c>
       <c r="B2139" t="inlineStr">
         <is>
-          <t>1927.00</t>
+          <t>1921.00</t>
         </is>
       </c>
       <c r="C2139" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>271.00</t>
+          <t>266.00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>871.00</t>
+          <t>831.00</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>800.00</t>
+          <t>794.00</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>512.00</t>
+          <t>507.00</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>534.00</t>
+          <t>533.00</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>158.00</t>
+          <t>153.00</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>2647.00</t>
+          <t>2597.00</t>
         </is>
       </c>
       <c r="C1639" t="inlineStr">
@@ -42632,7 +42632,7 @@
       </c>
       <c r="B1919" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>98.00</t>
         </is>
       </c>
       <c r="C1919" t="inlineStr">
@@ -42852,7 +42852,7 @@
       </c>
       <c r="B1929" t="inlineStr">
         <is>
-          <t>222.00</t>
+          <t>214.00</t>
         </is>
       </c>
       <c r="C1929" t="inlineStr">
@@ -44524,7 +44524,7 @@
       </c>
       <c r="B2005" t="inlineStr">
         <is>
-          <t>419.00</t>
+          <t>404.00</t>
         </is>
       </c>
       <c r="C2005" t="inlineStr">
@@ -45668,7 +45668,7 @@
       </c>
       <c r="B2057" t="inlineStr">
         <is>
-          <t>183.00</t>
+          <t>173.00</t>
         </is>
       </c>
       <c r="C2057" t="inlineStr">
@@ -47054,7 +47054,7 @@
       </c>
       <c r="B2120" t="inlineStr">
         <is>
-          <t>527.00</t>
+          <t>526.00</t>
         </is>
       </c>
       <c r="C2120" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>781.00</t>
+          <t>780.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47494,7 +47494,7 @@
       </c>
       <c r="B2140" t="inlineStr">
         <is>
-          <t>1921.00</t>
+          <t>1910.00</t>
         </is>
       </c>
       <c r="C2140" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>77.00</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>331.00</t>
+          <t>307.00</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>252.00</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>344.00</t>
+          <t>343.00</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="C1352" t="inlineStr">
@@ -33788,7 +33788,7 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>519.00</t>
+          <t>489.00</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
@@ -34162,7 +34162,7 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>133.00</t>
+          <t>129.00</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="C1549" t="inlineStr">
@@ -35614,7 +35614,7 @@
       </c>
       <c r="B1600" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C1600" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>44.00</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="C1604" t="inlineStr">
@@ -35922,7 +35922,7 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>109.00</t>
+          <t>106.00</t>
         </is>
       </c>
       <c r="C1614" t="inlineStr">
@@ -43072,7 +43072,7 @@
       </c>
       <c r="B1939" t="inlineStr">
         <is>
-          <t>749.00</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="C1939" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>490.00</t>
+          <t>470.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -14670,7 +14670,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>232.00</t>
+          <t>202.00</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -20214,7 +20214,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>367.00</t>
+          <t>337.00</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>794.00</t>
+          <t>793.00</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
@@ -31676,7 +31676,7 @@
       </c>
       <c r="B1421" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C1421" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="B1736" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="C1736" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="B1737" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1737" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="B1823" t="inlineStr">
         <is>
-          <t>157.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="C1823" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>328.00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>101.00</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>126.00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>1426.00</t>
+          <t>1423.00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>59.00</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>790.00</t>
+          <t>774.00</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>360.00</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>479.14</t>
+          <t>468.84</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>5168.00</t>
+          <t>5162.00</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>307.00</t>
+          <t>283.00</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>1166.00</t>
+          <t>1164.00</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>793.00</t>
+          <t>731.00</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -21468,7 +21468,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1164.00</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>177.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>489.60</t>
+          <t>481.80</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>252.00</t>
+          <t>247.00</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="B1049" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C1049" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C1050" t="inlineStr">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>514.00</t>
+          <t>491.00</t>
         </is>
       </c>
       <c r="C1083" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="B1233" t="inlineStr">
         <is>
-          <t>750.00</t>
+          <t>726.00</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="B1234" t="inlineStr">
         <is>
-          <t>1670.00</t>
+          <t>1646.00</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>1997.00</t>
+          <t>1973.00</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>821.00</t>
+          <t>797.00</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>230.00</t>
+          <t>206.00</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>991.00</t>
+          <t>967.00</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>147.00</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
@@ -29168,7 +29168,7 @@
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -29190,7 +29190,7 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>351.00</t>
+          <t>291.00</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
@@ -29212,7 +29212,7 @@
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>162.00</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr">
@@ -29718,7 +29718,7 @@
       </c>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>337.00</t>
+          <t>325.00</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr">
@@ -29806,7 +29806,7 @@
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>453.00</t>
+          <t>451.00</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>130.00</t>
+          <t>128.00</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr">
@@ -30840,7 +30840,7 @@
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>255.00</t>
+          <t>243.00</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="B1384" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>268.00</t>
         </is>
       </c>
       <c r="C1384" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>647.00</t>
+          <t>641.00</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr">
@@ -30950,7 +30950,7 @@
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>634.00</t>
+          <t>628.00</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>258.00</t>
+          <t>246.00</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr">
@@ -31148,7 +31148,7 @@
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>146.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
@@ -33788,7 +33788,7 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>489.00</t>
+          <t>455.00</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
@@ -33898,7 +33898,7 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
@@ -34162,7 +34162,7 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>129.00</t>
+          <t>99.00</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
@@ -34184,7 +34184,7 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>555.00</t>
+          <t>553.00</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
@@ -35900,7 +35900,7 @@
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>109.00</t>
+          <t>108.00</t>
         </is>
       </c>
       <c r="C1613" t="inlineStr">
@@ -36010,12 +36010,12 @@
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="C1618" t="inlineStr">
         <is>
-          <t>670.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="D1618" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>13414.00</t>
+          <t>13374.00</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>1171.00</t>
+          <t>1161.00</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>295.00</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
@@ -36978,7 +36978,7 @@
       </c>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>5263.00</t>
+          <t>5249.00</t>
         </is>
       </c>
       <c r="C1662" t="inlineStr">
@@ -37968,7 +37968,7 @@
       </c>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>276.00</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>57.00</t>
         </is>
       </c>
       <c r="C1739" t="inlineStr">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="B1811" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>256.00</t>
         </is>
       </c>
       <c r="C1811" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="B1823" t="inlineStr">
         <is>
-          <t>152.00</t>
+          <t>144.00</t>
         </is>
       </c>
       <c r="C1823" t="inlineStr">
@@ -40542,7 +40542,7 @@
       </c>
       <c r="B1824" t="inlineStr">
         <is>
-          <t>206.00</t>
+          <t>204.00</t>
         </is>
       </c>
       <c r="C1824" t="inlineStr">
@@ -42500,7 +42500,7 @@
       </c>
       <c r="B1913" t="inlineStr">
         <is>
-          <t>3590.00</t>
+          <t>3566.00</t>
         </is>
       </c>
       <c r="C1913" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="B1934" t="inlineStr">
         <is>
-          <t>684.00</t>
+          <t>564.00</t>
         </is>
       </c>
       <c r="C1934" t="inlineStr">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="B1937" t="inlineStr">
         <is>
-          <t>1121.00</t>
+          <t>1115.00</t>
         </is>
       </c>
       <c r="C1937" t="inlineStr">
@@ -43050,7 +43050,7 @@
       </c>
       <c r="B1938" t="inlineStr">
         <is>
-          <t>266.00</t>
+          <t>262.00</t>
         </is>
       </c>
       <c r="C1938" t="inlineStr">
@@ -43270,7 +43270,7 @@
       </c>
       <c r="B1948" t="inlineStr">
         <is>
-          <t>625.00</t>
+          <t>619.00</t>
         </is>
       </c>
       <c r="C1948" t="inlineStr">
@@ -44238,7 +44238,7 @@
       </c>
       <c r="B1992" t="inlineStr">
         <is>
-          <t>323.00</t>
+          <t>318.00</t>
         </is>
       </c>
       <c r="C1992" t="inlineStr">
@@ -44920,7 +44920,7 @@
       </c>
       <c r="B2023" t="inlineStr">
         <is>
-          <t>567.00</t>
+          <t>565.00</t>
         </is>
       </c>
       <c r="C2023" t="inlineStr">
@@ -45492,7 +45492,7 @@
       </c>
       <c r="B2049" t="inlineStr">
         <is>
-          <t>2931.00</t>
+          <t>2925.00</t>
         </is>
       </c>
       <c r="C2049" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="B2052" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C2052" t="inlineStr">
@@ -45580,7 +45580,7 @@
       </c>
       <c r="B2053" t="inlineStr">
         <is>
-          <t>238.00</t>
+          <t>236.00</t>
         </is>
       </c>
       <c r="C2053" t="inlineStr">
@@ -45602,7 +45602,7 @@
       </c>
       <c r="B2054" t="inlineStr">
         <is>
-          <t>206.00</t>
+          <t>202.00</t>
         </is>
       </c>
       <c r="C2054" t="inlineStr">
@@ -45690,7 +45690,7 @@
       </c>
       <c r="B2058" t="inlineStr">
         <is>
-          <t>293.00</t>
+          <t>263.00</t>
         </is>
       </c>
       <c r="C2058" t="inlineStr">
@@ -46086,7 +46086,7 @@
       </c>
       <c r="B2076" t="inlineStr">
         <is>
-          <t>46.00</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="C2076" t="inlineStr">
@@ -46174,7 +46174,7 @@
       </c>
       <c r="B2080" t="inlineStr">
         <is>
-          <t>843.00</t>
+          <t>841.00</t>
         </is>
       </c>
       <c r="C2080" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B2081" t="inlineStr">
         <is>
-          <t>673.00</t>
+          <t>670.00</t>
         </is>
       </c>
       <c r="C2081" t="inlineStr">
@@ -46306,7 +46306,7 @@
       </c>
       <c r="B2086" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="C2086" t="inlineStr">
@@ -46790,7 +46790,7 @@
       </c>
       <c r="B2108" t="inlineStr">
         <is>
-          <t>1129.00</t>
+          <t>1125.00</t>
         </is>
       </c>
       <c r="C2108" t="inlineStr">
@@ -46812,7 +46812,7 @@
       </c>
       <c r="B2109" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>77.00</t>
         </is>
       </c>
       <c r="C2109" t="inlineStr">
@@ -46966,7 +46966,7 @@
       </c>
       <c r="B2116" t="inlineStr">
         <is>
-          <t>230.00</t>
+          <t>229.00</t>
         </is>
       </c>
       <c r="C2116" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>470.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>2538.00</t>
+          <t>2528.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47142,7 +47142,7 @@
       </c>
       <c r="B2124" t="inlineStr">
         <is>
-          <t>1052.00</t>
+          <t>1051.00</t>
         </is>
       </c>
       <c r="C2124" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>774.00</t>
+          <t>773.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>1157.00</t>
+          <t>1156.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>2403.00</t>
+          <t>2401.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>324.00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>117.00</t>
+          <t>111.00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>294.00</t>
+          <t>214.00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2601.00</t>
+          <t>2561.00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>71.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>208.00</t>
+          <t>202.00</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>202.00</t>
+          <t>196.00</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>271.00</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>74.00</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>5162.00</t>
+          <t>5042.00</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>297.00</t>
+          <t>277.00</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>335.00</t>
+          <t>315.00</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -18828,7 +18828,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>396.00</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -19488,12 +19488,12 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>45.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>380.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>53.00</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>147.00</t>
+          <t>144.00</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>133.00</t>
+          <t>128.00</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>571.00</t>
+          <t>371.00</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>731.00</t>
+          <t>685.00</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -22238,7 +22238,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>537.00</t>
+          <t>487.00</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>9658.50</t>
+          <t>9657.50</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>247.00</t>
+          <t>199.00</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>77.00</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>59.00</t>
+          <t>58.00</t>
         </is>
       </c>
       <c r="C1070" t="inlineStr">
@@ -24394,7 +24394,7 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
@@ -24878,7 +24878,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>1254.00</t>
+          <t>1218.00</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
@@ -25340,7 +25340,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>4335.00</t>
+          <t>4310.00</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
@@ -25472,7 +25472,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>56.40</t>
+          <t>53.40</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="B1187" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>1520.00</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="B1188" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="B1204" t="inlineStr">
         <is>
-          <t>468.00</t>
+          <t>456.00</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
@@ -27650,7 +27650,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>797.00</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>206.00</t>
+          <t>106.00</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="B1240" t="inlineStr">
         <is>
-          <t>967.00</t>
+          <t>917.00</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>212.00</t>
+          <t>112.00</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr">
@@ -30290,7 +30290,7 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="B1360" t="inlineStr">
         <is>
-          <t>74.00</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="C1360" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C1380" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>641.00</t>
+          <t>617.00</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr">
@@ -33744,7 +33744,7 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>157.00</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
@@ -33788,7 +33788,7 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>455.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C1517" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>1010.00</t>
+          <t>686.00</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>486.00</t>
+          <t>438.00</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
@@ -34558,7 +34558,7 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>949.00</t>
+          <t>889.00</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
@@ -34954,7 +34954,7 @@
       </c>
       <c r="B1570" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C1570" t="inlineStr">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>123.00</t>
+          <t>113.00</t>
         </is>
       </c>
       <c r="C1580" t="inlineStr">
@@ -35394,7 +35394,7 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C1590" t="inlineStr">
@@ -35482,7 +35482,7 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="C1594" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
@@ -35658,7 +35658,7 @@
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>313.00</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="C1602" t="inlineStr">
@@ -35856,7 +35856,7 @@
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1611" t="inlineStr">
@@ -35944,7 +35944,7 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C1615" t="inlineStr">
@@ -35966,7 +35966,7 @@
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="C1616" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>11836.00</t>
+          <t>11716.00</t>
         </is>
       </c>
       <c r="C1639" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>13374.00</t>
+          <t>13214.00</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
@@ -36978,7 +36978,7 @@
       </c>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>5249.00</t>
+          <t>5209.00</t>
         </is>
       </c>
       <c r="C1662" t="inlineStr">
@@ -37396,7 +37396,7 @@
       </c>
       <c r="B1681" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="C1681" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>338.25</t>
+          <t>332.25</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
@@ -38342,7 +38342,7 @@
       </c>
       <c r="B1724" t="inlineStr">
         <is>
-          <t>133.00</t>
+          <t>97.00</t>
         </is>
       </c>
       <c r="C1724" t="inlineStr">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="B1814" t="inlineStr">
         <is>
-          <t>211.00</t>
+          <t>131.00</t>
         </is>
       </c>
       <c r="C1814" t="inlineStr">
@@ -40344,7 +40344,7 @@
       </c>
       <c r="B1815" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>260.00</t>
         </is>
       </c>
       <c r="C1815" t="inlineStr">
@@ -40542,7 +40542,7 @@
       </c>
       <c r="B1824" t="inlineStr">
         <is>
-          <t>204.00</t>
+          <t>189.00</t>
         </is>
       </c>
       <c r="C1824" t="inlineStr">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="B1914" t="inlineStr">
         <is>
-          <t>1413.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="C1914" t="inlineStr">
@@ -43160,7 +43160,7 @@
       </c>
       <c r="B1943" t="inlineStr">
         <is>
-          <t>1163.00</t>
+          <t>1113.00</t>
         </is>
       </c>
       <c r="C1943" t="inlineStr">
@@ -43270,7 +43270,7 @@
       </c>
       <c r="B1948" t="inlineStr">
         <is>
-          <t>619.00</t>
+          <t>519.00</t>
         </is>
       </c>
       <c r="C1948" t="inlineStr">
@@ -43424,7 +43424,7 @@
       </c>
       <c r="B1955" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="C1955" t="inlineStr">
@@ -43446,7 +43446,7 @@
       </c>
       <c r="B1956" t="inlineStr">
         <is>
-          <t>164.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="C1956" t="inlineStr">
@@ -44392,7 +44392,7 @@
       </c>
       <c r="B1999" t="inlineStr">
         <is>
-          <t>229.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="C1999" t="inlineStr">
@@ -44964,7 +44964,7 @@
       </c>
       <c r="B2025" t="inlineStr">
         <is>
-          <t>740.00</t>
+          <t>734.00</t>
         </is>
       </c>
       <c r="C2025" t="inlineStr">
@@ -45030,7 +45030,7 @@
       </c>
       <c r="B2028" t="inlineStr">
         <is>
-          <t>517.00</t>
+          <t>458.00</t>
         </is>
       </c>
       <c r="C2028" t="inlineStr">
@@ -45690,7 +45690,7 @@
       </c>
       <c r="B2058" t="inlineStr">
         <is>
-          <t>263.00</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="C2058" t="inlineStr">
@@ -46086,7 +46086,7 @@
       </c>
       <c r="B2076" t="inlineStr">
         <is>
-          <t>45.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="C2076" t="inlineStr">
@@ -46372,7 +46372,7 @@
       </c>
       <c r="B2089" t="inlineStr">
         <is>
-          <t>104.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C2089" t="inlineStr">
@@ -46922,7 +46922,7 @@
       </c>
       <c r="B2114" t="inlineStr">
         <is>
-          <t>444.00</t>
+          <t>443.00</t>
         </is>
       </c>
       <c r="C2114" t="inlineStr">
@@ -46944,7 +46944,7 @@
       </c>
       <c r="B2115" t="inlineStr">
         <is>
-          <t>511.00</t>
+          <t>501.00</t>
         </is>
       </c>
       <c r="C2115" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>450.00</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>740.00</t>
+          <t>716.00</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">
@@ -47142,7 +47142,7 @@
       </c>
       <c r="B2124" t="inlineStr">
         <is>
-          <t>1051.00</t>
+          <t>1031.00</t>
         </is>
       </c>
       <c r="C2124" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>773.00</t>
+          <t>727.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>1156.00</t>
+          <t>1116.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>2401.00</t>
+          <t>2323.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>77.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>120.00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>1284.00</t>
+          <t>1283.00</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>66.00</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>152.00</t>
+          <t>146.00</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>322.00</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>286.00</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>196.00</t>
+          <t>194.00</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>59.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>2993.00</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>3232.00</t>
+          <t>3214.00</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>2908.00</t>
+          <t>2885.00</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>470.00</t>
+          <t>466.00</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>5042.00</t>
+          <t>4922.00</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>277.00</t>
+          <t>265.00</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>396.00</t>
+          <t>378.00</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>197.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>185.00</t>
+          <t>184.00</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>677.00</t>
+          <t>627.00</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>1164.00</t>
+          <t>1104.00</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>199.00</t>
+          <t>173.00</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -23778,7 +23778,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>333.00</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>58.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>249.00</t>
+          <t>241.00</t>
         </is>
       </c>
       <c r="C1078" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>4300.00</t>
+          <t>4292.00</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>976.00</t>
+          <t>972.00</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>704.00</t>
+          <t>693.00</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
@@ -28244,7 +28244,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>1343.00</t>
+          <t>1336.00</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="B1281" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C1281" t="inlineStr">
@@ -28618,7 +28618,7 @@
       </c>
       <c r="B1282" t="inlineStr">
         <is>
-          <t>125.00</t>
+          <t>116.00</t>
         </is>
       </c>
       <c r="C1282" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>112.00</t>
+          <t>88.00</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr">
@@ -31478,7 +31478,7 @@
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>490.00</t>
+          <t>484.00</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
@@ -32336,7 +32336,7 @@
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
@@ -32710,7 +32710,7 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr">
@@ -33810,7 +33810,7 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
@@ -33854,7 +33854,7 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>541.00</t>
+          <t>481.00</t>
         </is>
       </c>
       <c r="C1520" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>553.00</t>
+          <t>550.00</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
@@ -34668,7 +34668,7 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>110.00</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>299.00</t>
         </is>
       </c>
       <c r="C1617" t="inlineStr">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>1161.00</t>
+          <t>1111.00</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
@@ -37990,7 +37990,7 @@
       </c>
       <c r="B1708" t="inlineStr">
         <is>
-          <t>276.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="C1708" t="inlineStr">
@@ -41048,7 +41048,7 @@
       </c>
       <c r="B1847" t="inlineStr">
         <is>
-          <t>299.00</t>
+          <t>297.00</t>
         </is>
       </c>
       <c r="C1847" t="inlineStr">
@@ -42940,7 +42940,7 @@
       </c>
       <c r="B1933" t="inlineStr">
         <is>
-          <t>3543.00</t>
+          <t>3243.00</t>
         </is>
       </c>
       <c r="C1933" t="inlineStr">
@@ -43160,7 +43160,7 @@
       </c>
       <c r="B1943" t="inlineStr">
         <is>
-          <t>114.00</t>
+          <t>110.00</t>
         </is>
       </c>
       <c r="C1943" t="inlineStr">
@@ -43270,7 +43270,7 @@
       </c>
       <c r="B1948" t="inlineStr">
         <is>
-          <t>147.00</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="C1948" t="inlineStr">
@@ -43468,7 +43468,7 @@
       </c>
       <c r="B1957" t="inlineStr">
         <is>
-          <t>152.00</t>
+          <t>139.00</t>
         </is>
       </c>
       <c r="C1957" t="inlineStr">
@@ -44986,7 +44986,7 @@
       </c>
       <c r="B2026" t="inlineStr">
         <is>
-          <t>734.00</t>
+          <t>726.00</t>
         </is>
       </c>
       <c r="C2026" t="inlineStr">
@@ -45338,7 +45338,7 @@
       </c>
       <c r="B2042" t="inlineStr">
         <is>
-          <t>1088.00</t>
+          <t>1085.00</t>
         </is>
       </c>
       <c r="C2042" t="inlineStr">
@@ -45624,7 +45624,7 @@
       </c>
       <c r="B2055" t="inlineStr">
         <is>
-          <t>202.00</t>
+          <t>199.00</t>
         </is>
       </c>
       <c r="C2055" t="inlineStr">
@@ -45712,12 +45712,12 @@
       </c>
       <c r="B2059" t="inlineStr">
         <is>
-          <t>53.00</t>
+          <t>403.00</t>
         </is>
       </c>
       <c r="C2059" t="inlineStr">
         <is>
-          <t>735.00</t>
+          <t>730.00</t>
         </is>
       </c>
       <c r="D2059" t="inlineStr">
@@ -45734,7 +45734,7 @@
       </c>
       <c r="B2060" t="inlineStr">
         <is>
-          <t>115.00</t>
+          <t>113.00</t>
         </is>
       </c>
       <c r="C2060" t="inlineStr">
@@ -45954,7 +45954,7 @@
       </c>
       <c r="B2070" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="C2070" t="inlineStr">
@@ -46218,7 +46218,7 @@
       </c>
       <c r="B2082" t="inlineStr">
         <is>
-          <t>670.00</t>
+          <t>661.00</t>
         </is>
       </c>
       <c r="C2082" t="inlineStr">
@@ -46240,7 +46240,7 @@
       </c>
       <c r="B2083" t="inlineStr">
         <is>
-          <t>293.00</t>
+          <t>281.00</t>
         </is>
       </c>
       <c r="C2083" t="inlineStr">
@@ -46570,7 +46570,7 @@
       </c>
       <c r="B2098" t="inlineStr">
         <is>
-          <t>253.00</t>
+          <t>247.00</t>
         </is>
       </c>
       <c r="C2098" t="inlineStr">
@@ -46592,7 +46592,7 @@
       </c>
       <c r="B2099" t="inlineStr">
         <is>
-          <t>938.00</t>
+          <t>932.00</t>
         </is>
       </c>
       <c r="C2099" t="inlineStr">
@@ -46746,7 +46746,7 @@
       </c>
       <c r="B2106" t="inlineStr">
         <is>
-          <t>129.00</t>
+          <t>123.00</t>
         </is>
       </c>
       <c r="C2106" t="inlineStr">
@@ -46768,7 +46768,7 @@
       </c>
       <c r="B2107" t="inlineStr">
         <is>
-          <t>1262.00</t>
+          <t>1256.00</t>
         </is>
       </c>
       <c r="C2107" t="inlineStr">
@@ -46790,7 +46790,7 @@
       </c>
       <c r="B2108" t="inlineStr">
         <is>
-          <t>2502.00</t>
+          <t>2487.00</t>
         </is>
       </c>
       <c r="C2108" t="inlineStr">
@@ -46944,7 +46944,7 @@
       </c>
       <c r="B2115" t="inlineStr">
         <is>
-          <t>443.00</t>
+          <t>433.00</t>
         </is>
       </c>
       <c r="C2115" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>874.00</t>
+          <t>870.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>392.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>1031.00</t>
+          <t>1001.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>677.00</t>
+          <t>671.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>727.00</t>
+          <t>715.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>1116.00</t>
+          <t>1070.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">
@@ -47252,7 +47252,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>2323.00</t>
+          <t>2293.00</t>
         </is>
       </c>
       <c r="C2129" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>580.00</t>
+          <t>576.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>324.00</t>
+          <t>309.00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>407.00</t>
+          <t>335.00</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>508.00</t>
+          <t>504.00</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>71.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>627.00</t>
+          <t>618.00</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>167.00</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -22502,7 +22502,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>249.00</t>
+          <t>241.00</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -22590,7 +22590,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>646.00</t>
+          <t>634.00</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
@@ -23778,7 +23778,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>327.00</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="B1071" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="C1071" t="inlineStr">
@@ -24394,7 +24394,7 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>569.00</t>
+          <t>568.00</t>
         </is>
       </c>
       <c r="C1090" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>4292.00</t>
+          <t>4280.00</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
@@ -26682,7 +26682,7 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="B1196" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>681.00</t>
+          <t>669.00</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>1347.00</t>
+          <t>1292.00</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="C1352" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C1354" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="B1387" t="inlineStr">
         <is>
-          <t>627.00</t>
+          <t>615.00</t>
         </is>
       </c>
       <c r="C1387" t="inlineStr">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>145.00</t>
+          <t>139.00</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>158.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>550.00</t>
+          <t>525.00</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
@@ -35042,7 +35042,7 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>1469.00</t>
+          <t>1467.00</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>209.00</t>
+          <t>199.00</t>
         </is>
       </c>
       <c r="C1580" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>113.00</t>
+          <t>108.00</t>
         </is>
       </c>
       <c r="C1581" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>444.00</t>
+          <t>438.00</t>
         </is>
       </c>
       <c r="C1645" t="inlineStr">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>332.25</t>
+          <t>327.25</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>537.38</t>
+          <t>534.38</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
@@ -38848,7 +38848,7 @@
       </c>
       <c r="B1747" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>69.00</t>
         </is>
       </c>
       <c r="C1747" t="inlineStr">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="B1914" t="inlineStr">
         <is>
-          <t>3566.00</t>
+          <t>3516.00</t>
         </is>
       </c>
       <c r="C1914" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="B1915" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1313.00</t>
         </is>
       </c>
       <c r="C1915" t="inlineStr">
@@ -42610,7 +42610,7 @@
       </c>
       <c r="B1918" t="inlineStr">
         <is>
-          <t>340.00</t>
+          <t>336.00</t>
         </is>
       </c>
       <c r="C1918" t="inlineStr">
@@ -42874,7 +42874,7 @@
       </c>
       <c r="B1930" t="inlineStr">
         <is>
-          <t>1185.00</t>
+          <t>1149.00</t>
         </is>
       </c>
       <c r="C1930" t="inlineStr">
@@ -42984,7 +42984,7 @@
       </c>
       <c r="B1935" t="inlineStr">
         <is>
-          <t>564.00</t>
+          <t>552.00</t>
         </is>
       </c>
       <c r="C1935" t="inlineStr">
@@ -43468,7 +43468,7 @@
       </c>
       <c r="B1957" t="inlineStr">
         <is>
-          <t>139.00</t>
+          <t>137.00</t>
         </is>
       </c>
       <c r="C1957" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>870.00</t>
+          <t>860.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>392.00</t>
+          <t>381.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47142,7 +47142,7 @@
       </c>
       <c r="B2124" t="inlineStr">
         <is>
-          <t>716.00</t>
+          <t>715.00</t>
         </is>
       </c>
       <c r="C2124" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>1001.00</t>
+          <t>991.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>671.00</t>
+          <t>660.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>715.00</t>
+          <t>714.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>1070.00</t>
+          <t>1060.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">
@@ -47428,7 +47428,7 @@
       </c>
       <c r="B2137" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="C2137" t="inlineStr">
@@ -47516,7 +47516,7 @@
       </c>
       <c r="B2141" t="inlineStr">
         <is>
-          <t>410.00</t>
+          <t>401.00</t>
         </is>
       </c>
       <c r="C2141" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -7190,7 +7190,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>269.00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>1353.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>504.00</t>
+          <t>501.00</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>266.00</t>
+          <t>235.00</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>74.00</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -20236,7 +20236,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>337.00</t>
+          <t>334.00</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>65.00</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -22304,7 +22304,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>1575.00</t>
+          <t>1569.00</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -22832,7 +22832,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>9657.50</t>
+          <t>9652.50</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>481.80</t>
+          <t>473.80</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>1134.00</t>
+          <t>1116.00</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>266.00</t>
+          <t>254.00</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -26088,7 +26088,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>197.00</t>
+          <t>194.00</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>972.00</t>
+          <t>966.00</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>693.00</t>
+          <t>689.00</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
@@ -28244,7 +28244,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>1336.00</t>
+          <t>1326.00</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>290.00</t>
+          <t>287.00</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
@@ -29542,7 +29542,7 @@
       </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr">
@@ -31302,7 +31302,7 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>86.00</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="C1404" t="inlineStr">
@@ -33766,12 +33766,12 @@
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>49.00</t>
+          <t>849.00</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
@@ -33810,12 +33810,12 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>59.00</t>
         </is>
       </c>
       <c r="D1518" t="inlineStr">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>686.00</t>
+          <t>682.00</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
@@ -36142,7 +36142,7 @@
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>254.00</t>
+          <t>218.00</t>
         </is>
       </c>
       <c r="C1624" t="inlineStr">
@@ -36494,7 +36494,7 @@
       </c>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>11716.00</t>
+          <t>11636.00</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>13214.00</t>
+          <t>13198.00</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>327.25</t>
+          <t>325.25</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
@@ -45624,7 +45624,7 @@
       </c>
       <c r="B2055" t="inlineStr">
         <is>
-          <t>199.00</t>
+          <t>189.00</t>
         </is>
       </c>
       <c r="C2055" t="inlineStr">
@@ -46570,7 +46570,7 @@
       </c>
       <c r="B2098" t="inlineStr">
         <is>
-          <t>247.00</t>
+          <t>246.00</t>
         </is>
       </c>
       <c r="C2098" t="inlineStr">
@@ -46680,7 +46680,7 @@
       </c>
       <c r="B2103" t="inlineStr">
         <is>
-          <t>339.00</t>
+          <t>333.00</t>
         </is>
       </c>
       <c r="C2103" t="inlineStr">
@@ -46812,7 +46812,7 @@
       </c>
       <c r="B2109" t="inlineStr">
         <is>
-          <t>1125.00</t>
+          <t>1117.00</t>
         </is>
       </c>
       <c r="C2109" t="inlineStr">
@@ -46878,7 +46878,7 @@
       </c>
       <c r="B2112" t="inlineStr">
         <is>
-          <t>289.00</t>
+          <t>285.00</t>
         </is>
       </c>
       <c r="C2112" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="B2118" t="inlineStr">
         <is>
-          <t>318.00</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="C2118" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>860.00</t>
+          <t>859.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
@@ -47142,7 +47142,7 @@
       </c>
       <c r="B2124" t="inlineStr">
         <is>
-          <t>715.00</t>
+          <t>714.00</t>
         </is>
       </c>
       <c r="C2124" t="inlineStr">
@@ -47252,7 +47252,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>2293.00</t>
+          <t>2291.00</t>
         </is>
       </c>
       <c r="C2129" t="inlineStr">
@@ -47538,7 +47538,7 @@
       </c>
       <c r="B2142" t="inlineStr">
         <is>
-          <t>1907.00</t>
+          <t>1901.00</t>
         </is>
       </c>
       <c r="C2142" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>576.00</t>
+          <t>574.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>256.00</t>
+          <t>236.00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>57.00</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>452.00</t>
+          <t>422.00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>49.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>455.84</t>
+          <t>446.34</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>57.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>324.00</t>
+          <t>312.00</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
@@ -21468,7 +21468,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>618.00</t>
+          <t>613.00</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -22216,7 +22216,7 @@
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>314.00</t>
+          <t>306.00</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>9650.00</t>
+          <t>9646.00</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>473.80</t>
+          <t>445.80</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>3308.00</t>
+          <t>3208.00</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>68.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
@@ -34228,7 +34228,7 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>497.00</t>
+          <t>485.00</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C1595" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C1596" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C1617" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>2597.00</t>
+          <t>1997.00</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>1159.00</t>
+          <t>1109.00</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
@@ -39970,7 +39970,7 @@
       </c>
       <c r="B1798" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C1798" t="inlineStr">
@@ -42720,7 +42720,7 @@
       </c>
       <c r="B1923" t="inlineStr">
         <is>
-          <t>199.00</t>
+          <t>183.00</t>
         </is>
       </c>
       <c r="C1923" t="inlineStr">
@@ -45470,7 +45470,7 @@
       </c>
       <c r="B2048" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="C2048" t="inlineStr">
@@ -45492,7 +45492,7 @@
       </c>
       <c r="B2049" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C2049" t="inlineStr">
@@ -45646,7 +45646,7 @@
       </c>
       <c r="B2056" t="inlineStr">
         <is>
-          <t>189.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="C2056" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>236.00</t>
+          <t>210.00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>126.00</t>
+          <t>104.00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1220.00</t>
+          <t>1170.00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>1941.00</t>
+          <t>1891.00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>704.00</t>
+          <t>694.00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>465.00</t>
+          <t>440.00</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>998.00</t>
+          <t>996.00</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>716.00</t>
+          <t>566.00</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>446.34</t>
+          <t>431.76</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>271.00</t>
+          <t>263.00</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -16562,7 +16562,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>53.00</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>98.00</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>74.00</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>830.00</t>
+          <t>828.00</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>113.00</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>1164.00</t>
+          <t>1160.00</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -21468,7 +21468,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>613.00</t>
+          <t>612.00</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>1104.00</t>
+          <t>1004.00</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>1569.00</t>
+          <t>1561.00</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>69.00</t>
+          <t>59.00</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>87.00</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>9646.00</t>
+          <t>9643.00</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C1026" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>110.00</t>
+          <t>104.00</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -24922,7 +24922,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>1218.00</t>
+          <t>1168.00</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>53.40</t>
+          <t>51.40</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
@@ -25736,7 +25736,7 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>243.00</t>
+          <t>193.00</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -26110,7 +26110,7 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>194.00</t>
+          <t>192.00</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>74.00</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>1214.00</t>
+          <t>1114.00</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>1292.00</t>
+          <t>1192.00</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr">
@@ -28728,7 +28728,7 @@
       </c>
       <c r="B1287" t="inlineStr">
         <is>
-          <t>580.00</t>
+          <t>460.00</t>
         </is>
       </c>
       <c r="C1287" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>500.00</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>500.00</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="C1293" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>1085.00</t>
+          <t>965.00</t>
         </is>
       </c>
       <c r="C1294" t="inlineStr">
@@ -29652,7 +29652,7 @@
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>243.00</t>
+          <t>231.00</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr">
@@ -30906,7 +30906,7 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>268.00</t>
+          <t>256.00</t>
         </is>
       </c>
       <c r="C1386" t="inlineStr">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>122.00</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C1406" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>87.00</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
@@ -33128,7 +33128,7 @@
       </c>
       <c r="B1487" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C1487" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="B1489" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="C1489" t="inlineStr">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
@@ -33634,7 +33634,7 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1494.00</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>290.00</t>
+          <t>278.00</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>682.00</t>
+          <t>680.00</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
@@ -34118,7 +34118,7 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>523.00</t>
+          <t>487.00</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
@@ -34228,7 +34228,7 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>485.00</t>
+          <t>435.00</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>166.00</t>
+          <t>130.00</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>1467.00</t>
+          <t>1461.00</t>
         </is>
       </c>
       <c r="C1575" t="inlineStr">
@@ -35482,7 +35482,7 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C1594" t="inlineStr">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C1617" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>298.00</t>
+          <t>297.00</t>
         </is>
       </c>
       <c r="C1618" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>1109.00</t>
+          <t>1059.00</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>13198.00</t>
+          <t>13196.00</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
@@ -36868,7 +36868,7 @@
       </c>
       <c r="B1657" t="inlineStr">
         <is>
-          <t>183.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="C1657" t="inlineStr">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>4911.00</t>
+          <t>4907.00</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
@@ -37000,7 +37000,7 @@
       </c>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>59.00</t>
         </is>
       </c>
       <c r="C1663" t="inlineStr">
@@ -38914,7 +38914,7 @@
       </c>
       <c r="B1750" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>68.00</t>
         </is>
       </c>
       <c r="C1750" t="inlineStr">
@@ -38958,7 +38958,7 @@
       </c>
       <c r="B1752" t="inlineStr">
         <is>
-          <t>103.00</t>
+          <t>91.00</t>
         </is>
       </c>
       <c r="C1752" t="inlineStr">
@@ -42478,7 +42478,7 @@
       </c>
       <c r="B1912" t="inlineStr">
         <is>
-          <t>825.00</t>
+          <t>675.00</t>
         </is>
       </c>
       <c r="C1912" t="inlineStr">
@@ -42500,7 +42500,7 @@
       </c>
       <c r="B1913" t="inlineStr">
         <is>
-          <t>574.00</t>
+          <t>424.00</t>
         </is>
       </c>
       <c r="C1913" t="inlineStr">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="B1914" t="inlineStr">
         <is>
-          <t>2915.00</t>
+          <t>2865.00</t>
         </is>
       </c>
       <c r="C1914" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="B1915" t="inlineStr">
         <is>
-          <t>3516.00</t>
+          <t>3466.00</t>
         </is>
       </c>
       <c r="C1915" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="B1934" t="inlineStr">
         <is>
-          <t>3243.00</t>
+          <t>4243.00</t>
         </is>
       </c>
       <c r="C1934" t="inlineStr">
@@ -44106,7 +44106,7 @@
       </c>
       <c r="B1986" t="inlineStr">
         <is>
-          <t>706.00</t>
+          <t>646.00</t>
         </is>
       </c>
       <c r="C1986" t="inlineStr">
@@ -44458,7 +44458,7 @@
       </c>
       <c r="B2002" t="inlineStr">
         <is>
-          <t>134.00</t>
+          <t>130.00</t>
         </is>
       </c>
       <c r="C2002" t="inlineStr">
@@ -45536,7 +45536,7 @@
       </c>
       <c r="B2051" t="inlineStr">
         <is>
-          <t>2925.00</t>
+          <t>2923.00</t>
         </is>
       </c>
       <c r="C2051" t="inlineStr">
@@ -45624,7 +45624,7 @@
       </c>
       <c r="B2055" t="inlineStr">
         <is>
-          <t>232.00</t>
+          <t>231.00</t>
         </is>
       </c>
       <c r="C2055" t="inlineStr">
@@ -45646,7 +45646,7 @@
       </c>
       <c r="B2056" t="inlineStr">
         <is>
-          <t>185.00</t>
+          <t>184.00</t>
         </is>
       </c>
       <c r="C2056" t="inlineStr">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="B2066" t="inlineStr">
         <is>
-          <t>143.00</t>
+          <t>131.00</t>
         </is>
       </c>
       <c r="C2066" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="B2079" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C2079" t="inlineStr">
@@ -46812,7 +46812,7 @@
       </c>
       <c r="B2109" t="inlineStr">
         <is>
-          <t>2487.00</t>
+          <t>2481.00</t>
         </is>
       </c>
       <c r="C2109" t="inlineStr">
@@ -46834,7 +46834,7 @@
       </c>
       <c r="B2110" t="inlineStr">
         <is>
-          <t>1077.00</t>
+          <t>1051.00</t>
         </is>
       </c>
       <c r="C2110" t="inlineStr">
@@ -46966,7 +46966,7 @@
       </c>
       <c r="B2116" t="inlineStr">
         <is>
-          <t>433.00</t>
+          <t>427.00</t>
         </is>
       </c>
       <c r="C2116" t="inlineStr">
@@ -46988,7 +46988,7 @@
       </c>
       <c r="B2117" t="inlineStr">
         <is>
-          <t>489.00</t>
+          <t>483.00</t>
         </is>
       </c>
       <c r="C2117" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="B2118" t="inlineStr">
         <is>
-          <t>229.00</t>
+          <t>223.00</t>
         </is>
       </c>
       <c r="C2118" t="inlineStr">
@@ -47032,7 +47032,7 @@
       </c>
       <c r="B2119" t="inlineStr">
         <is>
-          <t>312.00</t>
+          <t>306.00</t>
         </is>
       </c>
       <c r="C2119" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>847.00</t>
+          <t>808.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>381.00</t>
+          <t>268.00</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">
@@ -47142,7 +47142,7 @@
       </c>
       <c r="B2124" t="inlineStr">
         <is>
-          <t>2528.00</t>
+          <t>2516.00</t>
         </is>
       </c>
       <c r="C2124" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>988.00</t>
+          <t>964.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>713.00</t>
+          <t>663.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">
@@ -47252,7 +47252,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>1056.00</t>
+          <t>956.00</t>
         </is>
       </c>
       <c r="C2129" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>2291.00</t>
+          <t>2191.00</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>77.00</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>141.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>108.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>445.80</t>
+          <t>441.50</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>294.20</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>173.00</t>
+          <t>162.00</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>4280.00</t>
+          <t>4275.00</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="B1183" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
@@ -26484,7 +26484,7 @@
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>44.00</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="B1202" t="inlineStr">
         <is>
-          <t>275.00</t>
+          <t>260.00</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>395.00</t>
+          <t>365.00</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>1494.00</t>
+          <t>1490.00</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>174.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
@@ -34228,12 +34228,12 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>435.00</t>
+          <t>2310.00</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="D1537" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>199.00</t>
+          <t>198.00</t>
         </is>
       </c>
       <c r="C1581" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>13196.00</t>
+          <t>13156.00</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
@@ -37022,7 +37022,7 @@
       </c>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>5209.00</t>
+          <t>5109.00</t>
         </is>
       </c>
       <c r="C1664" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>324.25</t>
+          <t>321.25</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
@@ -38078,7 +38078,7 @@
       </c>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>534.38</t>
+          <t>524.38</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
@@ -38210,7 +38210,7 @@
       </c>
       <c r="B1718" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="C1718" t="inlineStr">
@@ -38232,7 +38232,7 @@
       </c>
       <c r="B1719" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="C1719" t="inlineStr">
@@ -41158,7 +41158,7 @@
       </c>
       <c r="B1852" t="inlineStr">
         <is>
-          <t>278.00</t>
+          <t>274.00</t>
         </is>
       </c>
       <c r="C1852" t="inlineStr">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="B1854" t="inlineStr">
         <is>
-          <t>267.00</t>
+          <t>263.00</t>
         </is>
       </c>
       <c r="C1854" t="inlineStr">
@@ -42126,7 +42126,7 @@
       </c>
       <c r="B1896" t="inlineStr">
         <is>
-          <t>293.00</t>
+          <t>290.00</t>
         </is>
       </c>
       <c r="C1896" t="inlineStr">
@@ -43072,7 +43072,7 @@
       </c>
       <c r="B1939" t="inlineStr">
         <is>
-          <t>1113.00</t>
+          <t>1077.00</t>
         </is>
       </c>
       <c r="C1939" t="inlineStr">
@@ -43644,7 +43644,7 @@
       </c>
       <c r="B1965" t="inlineStr">
         <is>
-          <t>250.00</t>
+          <t>166.00</t>
         </is>
       </c>
       <c r="C1965" t="inlineStr">
@@ -43666,7 +43666,7 @@
       </c>
       <c r="B1966" t="inlineStr">
         <is>
-          <t>529.00</t>
+          <t>337.00</t>
         </is>
       </c>
       <c r="C1966" t="inlineStr">
@@ -43710,7 +43710,7 @@
       </c>
       <c r="B1968" t="inlineStr">
         <is>
-          <t>360.00</t>
+          <t>276.00</t>
         </is>
       </c>
       <c r="C1968" t="inlineStr">
@@ -44722,7 +44722,7 @@
       </c>
       <c r="B2014" t="inlineStr">
         <is>
-          <t>2092.00</t>
+          <t>2088.00</t>
         </is>
       </c>
       <c r="C2014" t="inlineStr">
@@ -46130,7 +46130,7 @@
       </c>
       <c r="B2078" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="C2078" t="inlineStr">
@@ -46218,7 +46218,7 @@
       </c>
       <c r="B2082" t="inlineStr">
         <is>
-          <t>841.00</t>
+          <t>835.00</t>
         </is>
       </c>
       <c r="C2082" t="inlineStr">
@@ -46240,7 +46240,7 @@
       </c>
       <c r="B2083" t="inlineStr">
         <is>
-          <t>661.00</t>
+          <t>655.00</t>
         </is>
       </c>
       <c r="C2083" t="inlineStr">
@@ -46658,7 +46658,7 @@
       </c>
       <c r="B2102" t="inlineStr">
         <is>
-          <t>1144.00</t>
+          <t>1114.00</t>
         </is>
       </c>
       <c r="C2102" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>268.00</t>
+          <t>218.00</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>964.00</t>
+          <t>959.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>663.00</t>
+          <t>633.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>2191.00</t>
+          <t>2181.00</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">
@@ -47560,7 +47560,7 @@
       </c>
       <c r="B2143" t="inlineStr">
         <is>
-          <t>1901.00</t>
+          <t>1879.00</t>
         </is>
       </c>
       <c r="C2143" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>574.00</t>
+          <t>534.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>550.00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1950.00</t>
+          <t>1925.00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>221.00</t>
+          <t>218.00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>36.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>187.00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>158.00</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>136.00</t>
+          <t>131.00</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -21468,7 +21468,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>612.00</t>
+          <t>609.00</t>
         </is>
       </c>
       <c r="C957" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>339.00</t>
+          <t>314.00</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>261.70</t>
+          <t>254.70</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -23360,7 +23360,7 @@
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>8000</t>
         </is>
       </c>
     </row>
@@ -23404,7 +23404,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="B1053" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="C1053" t="inlineStr">
@@ -23998,7 +23998,7 @@
       </c>
       <c r="B1072" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="C1072" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>346.00</t>
+          <t>321.00</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="B1189" t="inlineStr">
         <is>
-          <t>1520.00</t>
+          <t>1070.00</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>142.00</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="B1235" t="inlineStr">
         <is>
-          <t>726.00</t>
+          <t>721.00</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>1973.00</t>
+          <t>1969.00</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
@@ -27892,7 +27892,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>615.00</t>
+          <t>597.00</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
@@ -31544,7 +31544,7 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>430.00</t>
+          <t>405.00</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>152.00</t>
+          <t>146.00</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>680.00</t>
+          <t>630.00</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
@@ -37022,7 +37022,7 @@
       </c>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>5109.00</t>
+          <t>5091.00</t>
         </is>
       </c>
       <c r="C1664" t="inlineStr">
@@ -38694,7 +38694,7 @@
       </c>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="C1740" t="inlineStr">
@@ -44590,7 +44590,7 @@
       </c>
       <c r="B2008" t="inlineStr">
         <is>
-          <t>392.00</t>
+          <t>367.00</t>
         </is>
       </c>
       <c r="C2008" t="inlineStr">
@@ -45074,7 +45074,7 @@
       </c>
       <c r="B2030" t="inlineStr">
         <is>
-          <t>458.00</t>
+          <t>446.00</t>
         </is>
       </c>
       <c r="C2030" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="B2050" t="inlineStr">
         <is>
-          <t>144.00</t>
+          <t>143.00</t>
         </is>
       </c>
       <c r="C2050" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="B2052" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="C2052" t="inlineStr">
@@ -46218,7 +46218,7 @@
       </c>
       <c r="B2082" t="inlineStr">
         <is>
-          <t>835.00</t>
+          <t>830.00</t>
         </is>
       </c>
       <c r="C2082" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>218.00</t>
+          <t>214.00</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">
@@ -47230,7 +47230,7 @@
       </c>
       <c r="B2128" t="inlineStr">
         <is>
-          <t>633.00</t>
+          <t>629.00</t>
         </is>
       </c>
       <c r="C2128" t="inlineStr">
@@ -47252,7 +47252,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>956.00</t>
+          <t>916.00</t>
         </is>
       </c>
       <c r="C2129" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>2181.00</t>
+          <t>2141.00</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">
@@ -47538,7 +47538,7 @@
       </c>
       <c r="B2142" t="inlineStr">
         <is>
-          <t>401.00</t>
+          <t>399.00</t>
         </is>
       </c>
       <c r="C2142" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>534.00</t>
+          <t>554.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>521.00</t>
+          <t>511.00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>342.00</t>
+          <t>642.00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>235.00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>210.00</t>
+          <t>208.00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>87.00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>488.00</t>
+          <t>486.00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>176.00</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>335.00</t>
+          <t>705.00</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>17.50</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>185.00</t>
+          <t>178.00</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>103.00</t>
+          <t>101.00</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -18828,7 +18828,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>265.00</t>
+          <t>250.00</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>828.00</t>
+          <t>798.00</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>332.00</t>
+          <t>316.00</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>771.00</t>
+          <t>521.00</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>156.00</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>159.00</t>
+          <t>109.00</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -22612,12 +22612,12 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>634.00</t>
+          <t>1134.00</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>245.00</t>
+          <t>252.50</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>441.50</t>
+          <t>436.50</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="B1154" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>142.00</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
@@ -27628,12 +27628,12 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>1969.00</t>
+          <t>2969.00</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>45.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="D1237" t="inlineStr">
@@ -28046,7 +28046,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>74.00</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>584.00</t>
+          <t>484.00</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>425.00</t>
+          <t>265.00</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
@@ -28112,12 +28112,12 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>492.00</t>
+          <t>967.00</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>155.00</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -28134,12 +28134,12 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>736.00</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>135.00</t>
         </is>
       </c>
       <c r="D1260" t="inlineStr">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="B1399" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>137.00</t>
         </is>
       </c>
       <c r="C1399" t="inlineStr">
@@ -31456,7 +31456,7 @@
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>91.00</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>1490.00</t>
+          <t>1488.00</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>630.00</t>
+          <t>580.00</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>426.00</t>
+          <t>402.00</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>97.00</t>
+          <t>82.00</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
@@ -34228,7 +34228,7 @@
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>2310.00</t>
+          <t>2285.00</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>130.00</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
@@ -34712,7 +34712,7 @@
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>13156.00</t>
+          <t>13148.00</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
@@ -37726,7 +37726,7 @@
       </c>
       <c r="B1696" t="inlineStr">
         <is>
-          <t>640.00</t>
+          <t>636.00</t>
         </is>
       </c>
       <c r="C1696" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="B1703" t="inlineStr">
         <is>
-          <t>382.00</t>
+          <t>367.00</t>
         </is>
       </c>
       <c r="C1703" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="B1709" t="inlineStr">
         <is>
-          <t>274.00</t>
+          <t>273.00</t>
         </is>
       </c>
       <c r="C1709" t="inlineStr">
@@ -42412,7 +42412,7 @@
       </c>
       <c r="B1909" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1338.00</t>
         </is>
       </c>
       <c r="C1909" t="inlineStr">
@@ -43072,7 +43072,7 @@
       </c>
       <c r="B1939" t="inlineStr">
         <is>
-          <t>1077.00</t>
+          <t>1113.00</t>
         </is>
       </c>
       <c r="C1939" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="B1985" t="inlineStr">
         <is>
-          <t>474.00</t>
+          <t>434.00</t>
         </is>
       </c>
       <c r="C1985" t="inlineStr">
@@ -44282,7 +44282,7 @@
       </c>
       <c r="B1994" t="inlineStr">
         <is>
-          <t>318.00</t>
+          <t>315.00</t>
         </is>
       </c>
       <c r="C1994" t="inlineStr">
@@ -45008,7 +45008,7 @@
       </c>
       <c r="B2027" t="inlineStr">
         <is>
-          <t>726.00</t>
+          <t>722.00</t>
         </is>
       </c>
       <c r="C2027" t="inlineStr">
@@ -45646,7 +45646,7 @@
       </c>
       <c r="B2056" t="inlineStr">
         <is>
-          <t>184.00</t>
+          <t>181.00</t>
         </is>
       </c>
       <c r="C2056" t="inlineStr">
@@ -45822,7 +45822,7 @@
       </c>
       <c r="B2064" t="inlineStr">
         <is>
-          <t>313.00</t>
+          <t>303.00</t>
         </is>
       </c>
       <c r="C2064" t="inlineStr">
@@ -46438,7 +46438,7 @@
       </c>
       <c r="B2092" t="inlineStr">
         <is>
-          <t>107.00</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="C2092" t="inlineStr">
@@ -46658,7 +46658,7 @@
       </c>
       <c r="B2102" t="inlineStr">
         <is>
-          <t>1114.00</t>
+          <t>1112.00</t>
         </is>
       </c>
       <c r="C2102" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>808.00</t>
+          <t>807.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>959.00</t>
+          <t>958.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47252,7 +47252,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>916.00</t>
+          <t>915.00</t>
         </is>
       </c>
       <c r="C2129" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>2141.00</t>
+          <t>2139.00</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">
@@ -47362,7 +47362,7 @@
       </c>
       <c r="B2134" t="inlineStr">
         <is>
-          <t>87.00</t>
+          <t>86.00</t>
         </is>
       </c>
       <c r="C2134" t="inlineStr">
@@ -47406,7 +47406,7 @@
       </c>
       <c r="B2136" t="inlineStr">
         <is>
-          <t>182.00</t>
+          <t>180.00</t>
         </is>
       </c>
       <c r="C2136" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -20126,7 +20126,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>179.00</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>111.00</t>
+          <t>731.00</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -21644,7 +21644,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>156.00</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>162.00</t>
+          <t>412.00</t>
         </is>
       </c>
       <c r="C1027" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="B1069" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C1069" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>278.00</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
@@ -34074,7 +34074,7 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>120.00</t>
+          <t>408.00</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>402.00</t>
+          <t>522.00</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="B1598" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>89.00</t>
         </is>
       </c>
       <c r="C1598" t="inlineStr">
@@ -36318,7 +36318,7 @@
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>74.00</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="C1632" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="B1934" t="inlineStr">
         <is>
-          <t>4243.00</t>
+          <t>4193.00</t>
         </is>
       </c>
       <c r="C1934" t="inlineStr">
@@ -43204,7 +43204,7 @@
       </c>
       <c r="B1945" t="inlineStr">
         <is>
-          <t>1113.00</t>
+          <t>1063.00</t>
         </is>
       </c>
       <c r="C1945" t="inlineStr">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="B1949" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="C1949" t="inlineStr">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="B1950" t="inlineStr">
         <is>
-          <t>519.00</t>
+          <t>469.00</t>
         </is>
       </c>
       <c r="C1950" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>208.00</t>
+          <t>207.00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>18.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>138.00</t>
+          <t>133.00</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1348.00</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -14824,12 +14824,12 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>54.00</t>
+          <t>66.00</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>650.00</t>
+          <t>780.00</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>417.76</t>
+          <t>405.76</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>263.00</t>
+          <t>117.00</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -19136,7 +19136,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>58.00</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>290.00</t>
+          <t>242.00</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -22238,7 +22238,7 @@
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>109.00</t>
+          <t>101.00</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>9639.00</t>
+          <t>9638.00</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -25560,7 +25560,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>41.40</t>
+          <t>40.90</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="B1165" t="inlineStr">
         <is>
-          <t>254.00</t>
+          <t>250.00</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
@@ -27936,7 +27936,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>447.00</t>
+          <t>397.00</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>669.00</t>
+          <t>661.00</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>460.00</t>
+          <t>432.00</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>412.00</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
@@ -30136,7 +30136,7 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>349.00</t>
+          <t>345.00</t>
         </is>
       </c>
       <c r="C1351" t="inlineStr">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="B1413" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="C1413" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>152.00</t>
         </is>
       </c>
       <c r="C1529" t="inlineStr">
@@ -34074,7 +34074,7 @@
       </c>
       <c r="B1530" t="inlineStr">
         <is>
-          <t>1213.00</t>
+          <t>1205.00</t>
         </is>
       </c>
       <c r="C1530" t="inlineStr">
@@ -34162,7 +34162,7 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>487.00</t>
+          <t>511.00</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
@@ -34580,7 +34580,7 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>308.00</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
@@ -35042,7 +35042,7 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
@@ -35108,7 +35108,7 @@
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>1457.00</t>
+          <t>1458.00</t>
         </is>
       </c>
       <c r="C1577" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>108.00</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="C1584" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>297.00</t>
+          <t>292.00</t>
         </is>
       </c>
       <c r="C1620" t="inlineStr">
@@ -36626,7 +36626,7 @@
       </c>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>13068.00</t>
+          <t>12850.00</t>
         </is>
       </c>
       <c r="C1646" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>550.00</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
@@ -37066,7 +37066,7 @@
       </c>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>5071.00</t>
+          <t>5037.00</t>
         </is>
       </c>
       <c r="C1666" t="inlineStr">
@@ -37286,7 +37286,7 @@
       </c>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>1672.00</t>
+          <t>1660.00</t>
         </is>
       </c>
       <c r="C1676" t="inlineStr">
@@ -37550,7 +37550,7 @@
       </c>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>1112.00</t>
+          <t>712.00</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
@@ -40586,7 +40586,7 @@
       </c>
       <c r="B1826" t="inlineStr">
         <is>
-          <t>197.00</t>
+          <t>194.00</t>
         </is>
       </c>
       <c r="C1826" t="inlineStr">
@@ -43006,7 +43006,7 @@
       </c>
       <c r="B1936" t="inlineStr">
         <is>
-          <t>4189.00</t>
+          <t>4039.00</t>
         </is>
       </c>
       <c r="C1936" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="B2045" t="inlineStr">
         <is>
-          <t>1073.00</t>
+          <t>1049.00</t>
         </is>
       </c>
       <c r="C2045" t="inlineStr">
@@ -45668,7 +45668,7 @@
       </c>
       <c r="B2057" t="inlineStr">
         <is>
-          <t>231.00</t>
+          <t>223.00</t>
         </is>
       </c>
       <c r="C2057" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>231.00</t>
+          <t>217.00</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>405.76</t>
+          <t>402.26</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>384.00</t>
+          <t>382.00</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>93.00</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>459.00</t>
+          <t>447.00</t>
         </is>
       </c>
       <c r="C1076" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>736.00</t>
+          <t>734.00</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
@@ -34184,7 +34184,7 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
@@ -34250,7 +34250,7 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>2185.00</t>
+          <t>2181.00</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
@@ -34646,7 +34646,7 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>889.00</t>
+          <t>885.00</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="B1713" t="inlineStr">
         <is>
-          <t>320.25</t>
+          <t>315.25</t>
         </is>
       </c>
       <c r="C1713" t="inlineStr">
@@ -43116,7 +43116,7 @@
       </c>
       <c r="B1941" t="inlineStr">
         <is>
-          <t>1113.00</t>
+          <t>1109.00</t>
         </is>
       </c>
       <c r="C1941" t="inlineStr">
@@ -46944,7 +46944,7 @@
       </c>
       <c r="B2115" t="inlineStr">
         <is>
-          <t>285.00</t>
+          <t>280.00</t>
         </is>
       </c>
       <c r="C2115" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="B2118" t="inlineStr">
         <is>
-          <t>427.00</t>
+          <t>422.00</t>
         </is>
       </c>
       <c r="C2118" t="inlineStr">
@@ -47054,7 +47054,7 @@
       </c>
       <c r="B2120" t="inlineStr">
         <is>
-          <t>222.00</t>
+          <t>217.00</t>
         </is>
       </c>
       <c r="C2120" t="inlineStr">
@@ -47120,7 +47120,7 @@
       </c>
       <c r="B2123" t="inlineStr">
         <is>
-          <t>168.00</t>
+          <t>163.00</t>
         </is>
       </c>
       <c r="C2123" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>183.00</t>
+          <t>163.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>702.00</t>
+          <t>692.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>629.00</t>
+          <t>609.00</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">
@@ -47296,7 +47296,7 @@
       </c>
       <c r="B2131" t="inlineStr">
         <is>
-          <t>917.00</t>
+          <t>897.00</t>
         </is>
       </c>
       <c r="C2131" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="B2132" t="inlineStr">
         <is>
-          <t>2140.00</t>
+          <t>2120.00</t>
         </is>
       </c>
       <c r="C2132" t="inlineStr">
@@ -47362,7 +47362,7 @@
       </c>
       <c r="B2134" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>65.00</t>
         </is>
       </c>
       <c r="C2134" t="inlineStr">
@@ -47384,7 +47384,7 @@
       </c>
       <c r="B2135" t="inlineStr">
         <is>
-          <t>292.00</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="C2135" t="inlineStr">
@@ -47406,7 +47406,7 @@
       </c>
       <c r="B2136" t="inlineStr">
         <is>
-          <t>87.00</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="C2136" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>307.00</t>
+          <t>304.00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>511.00</t>
+          <t>488.00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1494.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>128.00</t>
+          <t>122.00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>253.00</t>
+          <t>217.00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>97.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>1283.00</t>
+          <t>1273.00</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>1348.00</t>
+          <t>1324.00</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>402.26</t>
+          <t>371.26</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>466.00</t>
+          <t>468.00</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>339.00</t>
+          <t>329.00</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>163.00</t>
+          <t>156.00</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>218.00</t>
+          <t>168.00</t>
         </is>
       </c>
       <c r="C909" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>128.00</t>
+          <t>126.00</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>242.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>608.00</t>
+          <t>598.00</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>487.00</t>
+          <t>412.00</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -22634,7 +22634,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>241.00</t>
+          <t>240.00</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>9638.00</t>
+          <t>9625.00</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>402.00</t>
+          <t>397.00</t>
         </is>
       </c>
       <c r="C1029" t="inlineStr">
@@ -23778,7 +23778,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C1062" t="inlineStr">
@@ -23800,7 +23800,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>42.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="C1063" t="inlineStr">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>322.00</t>
+          <t>320.00</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>4275.00</t>
+          <t>4274.00</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>268.00</t>
+          <t>267.00</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -26088,7 +26088,7 @@
       </c>
       <c r="B1167" t="inlineStr">
         <is>
-          <t>193.00</t>
+          <t>143.00</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>192.00</t>
+          <t>189.00</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>1070.00</t>
+          <t>870.00</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
@@ -27056,7 +27056,7 @@
       </c>
       <c r="B1211" t="inlineStr">
         <is>
-          <t>169.00</t>
+          <t>166.00</t>
         </is>
       </c>
       <c r="C1211" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="B1212" t="inlineStr">
         <is>
-          <t>135.00</t>
+          <t>134.00</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
@@ -29080,7 +29080,7 @@
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>220.00</t>
+          <t>205.00</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
@@ -30070,7 +30070,7 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>327.00</t>
+          <t>325.00</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>412.00</t>
+          <t>358.00</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>269.00</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr">
@@ -31720,12 +31720,12 @@
       </c>
       <c r="B1423" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>690.00</t>
+          <t>680.00</t>
         </is>
       </c>
       <c r="D1423" t="inlineStr">
@@ -31742,12 +31742,12 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>600.00</t>
+          <t>590.00</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
@@ -31764,12 +31764,12 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>32.00</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>510.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
@@ -32754,12 +32754,12 @@
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>690.00</t>
+          <t>680.00</t>
         </is>
       </c>
       <c r="D1470" t="inlineStr">
@@ -32776,12 +32776,12 @@
       </c>
       <c r="B1471" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>600.00</t>
+          <t>590.00</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
@@ -32798,12 +32798,12 @@
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>510.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="D1472" t="inlineStr">
@@ -33260,12 +33260,12 @@
       </c>
       <c r="B1493" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>350.00</t>
+          <t>320.00</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
@@ -33524,7 +33524,7 @@
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>154.00</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>83.00</t>
         </is>
       </c>
       <c r="C1506" t="inlineStr">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="B1509" t="inlineStr">
         <is>
-          <t>992.00</t>
+          <t>982.00</t>
         </is>
       </c>
       <c r="C1509" t="inlineStr">
@@ -33634,7 +33634,7 @@
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>1631.00</t>
+          <t>1621.00</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
@@ -33876,7 +33876,7 @@
       </c>
       <c r="B1521" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="C1521" t="inlineStr">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>580.00</t>
+          <t>576.00</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
@@ -34118,7 +34118,7 @@
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>408.00</t>
+          <t>410.00</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
@@ -34162,7 +34162,7 @@
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>511.00</t>
+          <t>506.00</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
@@ -35042,7 +35042,7 @@
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="B1580" t="inlineStr">
         <is>
-          <t>52.00</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="C1580" t="inlineStr">
@@ -35218,7 +35218,7 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>164.00</t>
+          <t>158.00</t>
         </is>
       </c>
       <c r="C1582" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>188.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="C1583" t="inlineStr">
@@ -35680,7 +35680,7 @@
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>211.00</t>
+          <t>208.00</t>
         </is>
       </c>
       <c r="C1603" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="B1606" t="inlineStr">
         <is>
-          <t>297.00</t>
+          <t>294.00</t>
         </is>
       </c>
       <c r="C1606" t="inlineStr">
@@ -35944,7 +35944,7 @@
       </c>
       <c r="B1615" t="inlineStr">
         <is>
-          <t>423.00</t>
+          <t>422.00</t>
         </is>
       </c>
       <c r="C1615" t="inlineStr">
@@ -36032,7 +36032,7 @@
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C1619" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>292.00</t>
+          <t>281.00</t>
         </is>
       </c>
       <c r="C1620" t="inlineStr">
@@ -36076,7 +36076,7 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="C1621" t="inlineStr">
@@ -36098,7 +36098,7 @@
       </c>
       <c r="B1622" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C1622" t="inlineStr">
@@ -36912,7 +36912,7 @@
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>550.00</t>
+          <t>530.00</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
@@ -37110,7 +37110,7 @@
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>98.00</t>
+          <t>94.00</t>
         </is>
       </c>
       <c r="C1668" t="inlineStr">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>4666.00</t>
+          <t>4630.00</t>
         </is>
       </c>
       <c r="C1672" t="inlineStr">
@@ -37418,7 +37418,7 @@
       </c>
       <c r="B1682" t="inlineStr">
         <is>
-          <t>1188.00</t>
+          <t>1088.00</t>
         </is>
       </c>
       <c r="C1682" t="inlineStr">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="B1711" t="inlineStr">
         <is>
-          <t>273.00</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="C1711" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="B1739" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="C1739" t="inlineStr">
@@ -38694,7 +38694,7 @@
       </c>
       <c r="B1740" t="inlineStr">
         <is>
-          <t>58.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C1740" t="inlineStr">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="B1811" t="inlineStr">
         <is>
-          <t>163.00</t>
+          <t>123.00</t>
         </is>
       </c>
       <c r="C1811" t="inlineStr">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="B1814" t="inlineStr">
         <is>
-          <t>310.00</t>
+          <t>200.00</t>
         </is>
       </c>
       <c r="C1814" t="inlineStr">
@@ -40366,7 +40366,7 @@
       </c>
       <c r="B1816" t="inlineStr">
         <is>
-          <t>372.00</t>
+          <t>222.00</t>
         </is>
       </c>
       <c r="C1816" t="inlineStr">
@@ -40388,7 +40388,7 @@
       </c>
       <c r="B1817" t="inlineStr">
         <is>
-          <t>638.00</t>
+          <t>238.00</t>
         </is>
       </c>
       <c r="C1817" t="inlineStr">
@@ -40432,7 +40432,7 @@
       </c>
       <c r="B1819" t="inlineStr">
         <is>
-          <t>260.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="C1819" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="B1820" t="inlineStr">
         <is>
-          <t>443.00</t>
+          <t>263.00</t>
         </is>
       </c>
       <c r="C1820" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="B1849" t="inlineStr">
         <is>
-          <t>71.00</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="C1849" t="inlineStr">
@@ -41378,7 +41378,7 @@
       </c>
       <c r="B1862" t="inlineStr">
         <is>
-          <t>486.00</t>
+          <t>484.00</t>
         </is>
       </c>
       <c r="C1862" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="B1915" t="inlineStr">
         <is>
-          <t>424.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="C1915" t="inlineStr">
@@ -42566,7 +42566,7 @@
       </c>
       <c r="B1916" t="inlineStr">
         <is>
-          <t>2815.00</t>
+          <t>2813.00</t>
         </is>
       </c>
       <c r="C1916" t="inlineStr">
@@ -43116,7 +43116,7 @@
       </c>
       <c r="B1941" t="inlineStr">
         <is>
-          <t>1109.00</t>
+          <t>1085.00</t>
         </is>
       </c>
       <c r="C1941" t="inlineStr">
@@ -43534,7 +43534,7 @@
       </c>
       <c r="B1960" t="inlineStr">
         <is>
-          <t>137.00</t>
+          <t>134.00</t>
         </is>
       </c>
       <c r="C1960" t="inlineStr">
@@ -43930,7 +43930,7 @@
       </c>
       <c r="B1978" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C1978" t="inlineStr">
@@ -44348,7 +44348,7 @@
       </c>
       <c r="B1997" t="inlineStr">
         <is>
-          <t>167.00</t>
+          <t>166.00</t>
         </is>
       </c>
       <c r="C1997" t="inlineStr">
@@ -44480,7 +44480,7 @@
       </c>
       <c r="B2003" t="inlineStr">
         <is>
-          <t>185.00</t>
+          <t>182.00</t>
         </is>
       </c>
       <c r="C2003" t="inlineStr">
@@ -44854,7 +44854,7 @@
       </c>
       <c r="B2020" t="inlineStr">
         <is>
-          <t>158.00</t>
+          <t>134.00</t>
         </is>
       </c>
       <c r="C2020" t="inlineStr">
@@ -45118,7 +45118,7 @@
       </c>
       <c r="B2032" t="inlineStr">
         <is>
-          <t>446.00</t>
+          <t>444.00</t>
         </is>
       </c>
       <c r="C2032" t="inlineStr">
@@ -45690,7 +45690,7 @@
       </c>
       <c r="B2058" t="inlineStr">
         <is>
-          <t>181.00</t>
+          <t>176.00</t>
         </is>
       </c>
       <c r="C2058" t="inlineStr">
@@ -45910,7 +45910,7 @@
       </c>
       <c r="B2068" t="inlineStr">
         <is>
-          <t>131.00</t>
+          <t>128.00</t>
         </is>
       </c>
       <c r="C2068" t="inlineStr">
@@ -46130,7 +46130,7 @@
       </c>
       <c r="B2078" t="inlineStr">
         <is>
-          <t>46.00</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="C2078" t="inlineStr">
@@ -46504,7 +46504,7 @@
       </c>
       <c r="B2095" t="inlineStr">
         <is>
-          <t>137.00</t>
+          <t>136.00</t>
         </is>
       </c>
       <c r="C2095" t="inlineStr">
@@ -46944,7 +46944,7 @@
       </c>
       <c r="B2115" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>278.00</t>
         </is>
       </c>
       <c r="C2115" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="B2118" t="inlineStr">
         <is>
-          <t>422.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="C2118" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>163.00</t>
+          <t>143.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="B2130" t="inlineStr">
         <is>
-          <t>609.00</t>
+          <t>608.00</t>
         </is>
       </c>
       <c r="C2130" t="inlineStr">
@@ -47296,7 +47296,7 @@
       </c>
       <c r="B2131" t="inlineStr">
         <is>
-          <t>897.00</t>
+          <t>891.00</t>
         </is>
       </c>
       <c r="C2131" t="inlineStr">
@@ -47472,7 +47472,7 @@
       </c>
       <c r="B2139" t="inlineStr">
         <is>
-          <t>154.00</t>
+          <t>149.00</t>
         </is>
       </c>
       <c r="C2139" t="inlineStr">
@@ -47516,7 +47516,7 @@
       </c>
       <c r="B2141" t="inlineStr">
         <is>
-          <t>53.00</t>
+          <t>52.00</t>
         </is>
       </c>
       <c r="C2141" t="inlineStr">
@@ -47604,7 +47604,7 @@
       </c>
       <c r="B2145" t="inlineStr">
         <is>
-          <t>1878.00</t>
+          <t>1860.00</t>
         </is>
       </c>
       <c r="C2145" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>554.00</t>
+          <t>552.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>304.00</t>
+          <t>302.00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>207.00</t>
+          <t>201.00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>122.00</t>
+          <t>117.00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>1423.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>139.00</t>
+          <t>109.00</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>566.00</t>
+          <t>546.00</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>58.00</t>
+          <t>52.00</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>418.00</t>
+          <t>338.00</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>181.00</t>
+          <t>151.00</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>70.00</t>
+          <t>68.00</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>46.00</t>
+          <t>42.00</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -17376,12 +17376,12 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>182.00</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>145.00</t>
+          <t>135.00</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>73.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>38.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>798.00</t>
+          <t>787.00</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>245.00</t>
+          <t>229.00</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>616.00</t>
+          <t>606.00</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>598.00</t>
+          <t>581.00</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>131.00</t>
+          <t>107.00</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>412.00</t>
+          <t>362.00</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>376.00</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>318.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>59.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
@@ -22656,7 +22656,7 @@
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>240.00</t>
+          <t>233.00</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
@@ -22678,7 +22678,7 @@
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>1134.00</t>
+          <t>1079.00</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>9624.00</t>
+          <t>9621.00</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>397.00</t>
+          <t>387.00</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>510.00</t>
+          <t>470.00</t>
         </is>
       </c>
       <c r="C1040" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>31.00</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="B1088" t="inlineStr">
         <is>
-          <t>441.00</t>
+          <t>341.00</t>
         </is>
       </c>
       <c r="C1088" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>567.00</t>
+          <t>544.00</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>250.00</t>
+          <t>240.00</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>487.00</t>
+          <t>485.00</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
@@ -25450,7 +25450,7 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>4274.00</t>
+          <t>4247.00</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
@@ -27166,7 +27166,7 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>966.00</t>
+          <t>936.00</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
@@ -29784,7 +29784,7 @@
       </c>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>344.00</t>
+          <t>244.00</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr">
@@ -30290,7 +30290,7 @@
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>52.00</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
@@ -33898,7 +33898,7 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
@@ -34338,7 +34338,7 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
@@ -34668,7 +34668,7 @@
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>885.00</t>
+          <t>879.00</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
@@ -34756,7 +34756,7 @@
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
@@ -35372,7 +35372,7 @@
       </c>
       <c r="B1589" t="inlineStr">
         <is>
-          <t>66.00</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="C1589" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>1997.00</t>
+          <t>1897.00</t>
         </is>
       </c>
       <c r="C1645" t="inlineStr">
@@ -37022,7 +37022,7 @@
       </c>
       <c r="B1664" t="inlineStr">
         <is>
-          <t>1111.00</t>
+          <t>1087.00</t>
         </is>
       </c>
       <c r="C1664" t="inlineStr">
@@ -38122,7 +38122,7 @@
       </c>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>315.25</t>
+          <t>295.25</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
@@ -39244,7 +39244,7 @@
       </c>
       <c r="B1765" t="inlineStr">
         <is>
-          <t>52.00</t>
+          <t>46.00</t>
         </is>
       </c>
       <c r="C1765" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="B1766" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="C1766" t="inlineStr">
@@ -40674,7 +40674,7 @@
       </c>
       <c r="B1830" t="inlineStr">
         <is>
-          <t>211.00</t>
+          <t>201.00</t>
         </is>
       </c>
       <c r="C1830" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="B1849" t="inlineStr">
         <is>
-          <t>216.00</t>
+          <t>168.00</t>
         </is>
       </c>
       <c r="C1849" t="inlineStr">
@@ -41114,7 +41114,7 @@
       </c>
       <c r="B1850" t="inlineStr">
         <is>
-          <t>55.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1850" t="inlineStr">
@@ -41224,7 +41224,7 @@
       </c>
       <c r="B1855" t="inlineStr">
         <is>
-          <t>274.00</t>
+          <t>226.00</t>
         </is>
       </c>
       <c r="C1855" t="inlineStr">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="B1917" t="inlineStr">
         <is>
-          <t>2813.00</t>
+          <t>2663.00</t>
         </is>
       </c>
       <c r="C1917" t="inlineStr">
@@ -42610,7 +42610,7 @@
       </c>
       <c r="B1918" t="inlineStr">
         <is>
-          <t>3416.00</t>
+          <t>3266.00</t>
         </is>
       </c>
       <c r="C1918" t="inlineStr">
@@ -43358,7 +43358,7 @@
       </c>
       <c r="B1952" t="inlineStr">
         <is>
-          <t>757.00</t>
+          <t>697.00</t>
         </is>
       </c>
       <c r="C1952" t="inlineStr">
@@ -44150,7 +44150,7 @@
       </c>
       <c r="B1988" t="inlineStr">
         <is>
-          <t>434.00</t>
+          <t>354.00</t>
         </is>
       </c>
       <c r="C1988" t="inlineStr">
@@ -44524,7 +44524,7 @@
       </c>
       <c r="B2005" t="inlineStr">
         <is>
-          <t>132.00</t>
+          <t>122.00</t>
         </is>
       </c>
       <c r="C2005" t="inlineStr">
@@ -44854,7 +44854,7 @@
       </c>
       <c r="B2020" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="C2020" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="B2033" t="inlineStr">
         <is>
-          <t>444.00</t>
+          <t>414.00</t>
         </is>
       </c>
       <c r="C2033" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="B2045" t="inlineStr">
         <is>
-          <t>394.00</t>
+          <t>382.00</t>
         </is>
       </c>
       <c r="C2045" t="inlineStr">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>353.00</t>
+          <t>323.00</t>
         </is>
       </c>
       <c r="C2063" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="B2079" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="C2079" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B2081" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C2081" t="inlineStr">
@@ -46856,7 +46856,7 @@
       </c>
       <c r="B2111" t="inlineStr">
         <is>
-          <t>1256.00</t>
+          <t>1251.00</t>
         </is>
       </c>
       <c r="C2111" t="inlineStr">
@@ -46878,7 +46878,7 @@
       </c>
       <c r="B2112" t="inlineStr">
         <is>
-          <t>2441.00</t>
+          <t>2436.00</t>
         </is>
       </c>
       <c r="C2112" t="inlineStr">
@@ -46900,7 +46900,7 @@
       </c>
       <c r="B2113" t="inlineStr">
         <is>
-          <t>1011.00</t>
+          <t>1006.00</t>
         </is>
       </c>
       <c r="C2113" t="inlineStr">
@@ -47032,7 +47032,7 @@
       </c>
       <c r="B2119" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>417.00</t>
         </is>
       </c>
       <c r="C2119" t="inlineStr">
@@ -47076,7 +47076,7 @@
       </c>
       <c r="B2121" t="inlineStr">
         <is>
-          <t>217.00</t>
+          <t>211.00</t>
         </is>
       </c>
       <c r="C2121" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>804.00</t>
+          <t>774.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>2516.00</t>
+          <t>2486.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47296,7 +47296,7 @@
       </c>
       <c r="B2131" t="inlineStr">
         <is>
-          <t>608.00</t>
+          <t>558.00</t>
         </is>
       </c>
       <c r="C2131" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="B2133" t="inlineStr">
         <is>
-          <t>2120.00</t>
+          <t>2070.00</t>
         </is>
       </c>
       <c r="C2133" t="inlineStr">
@@ -47472,7 +47472,7 @@
       </c>
       <c r="B2139" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>170.00</t>
         </is>
       </c>
       <c r="C2139" t="inlineStr">
@@ -47604,7 +47604,7 @@
       </c>
       <c r="B2145" t="inlineStr">
         <is>
-          <t>399.00</t>
+          <t>378.00</t>
         </is>
       </c>
       <c r="C2145" t="inlineStr">
@@ -47626,7 +47626,7 @@
       </c>
       <c r="B2146" t="inlineStr">
         <is>
-          <t>1860.00</t>
+          <t>1830.00</t>
         </is>
       </c>
       <c r="C2146" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>552.00</t>
+          <t>542.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Gate Lock 12B ATC (Laser Keys)</t>
+          <t>Gate Lock 12B 3M (Laser Keys)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1900</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>160.00</t>
+          <t>141.00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>52.00</t>
+          <t>49.00</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>788.00</t>
+          <t>786.00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>113.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>217.00</t>
+          <t>211.00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>753.00</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>98.00</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>133.00</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>119.00</t>
+          <t>107.00</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>308.00</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>1273.00</t>
+          <t>1263.00</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>375.00</t>
+          <t>315.00</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>52.00</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>362.00</t>
+          <t>317.00</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>66.00</t>
+          <t>64.00</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>22.00</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>68.00</t>
+          <t>64.00</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>901.00</t>
+          <t>881.00</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>4922.00</t>
+          <t>4762.00</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>522.00</t>
+          <t>497.00</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>229.00</t>
+          <t>219.00</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>606.00</t>
+          <t>456.00</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>581.00</t>
+          <t>579.00</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>1004.00</t>
+          <t>904.00</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>49.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>387.00</t>
+          <t>377.00</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>3208.00</t>
+          <t>3108.00</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -23690,7 +23690,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1058" t="inlineStr">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="C1059" t="inlineStr">
@@ -23866,7 +23866,7 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>317.00</t>
         </is>
       </c>
       <c r="C1066" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="B1075" t="inlineStr">
         <is>
-          <t>31.00</t>
+          <t>27.00</t>
         </is>
       </c>
       <c r="C1075" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>241.00</t>
+          <t>225.00</t>
         </is>
       </c>
       <c r="C1082" t="inlineStr">
@@ -24262,17 +24262,17 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160.00</t>
         </is>
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280.00</t>
         </is>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360</t>
         </is>
       </c>
     </row>
@@ -24328,7 +24328,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>1173.00</t>
+          <t>1151.00</t>
         </is>
       </c>
       <c r="C1087" t="inlineStr">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>544.00</t>
+          <t>540.00</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
@@ -25450,7 +25450,7 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>4247.00</t>
+          <t>4237.00</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
@@ -26110,7 +26110,7 @@
       </c>
       <c r="B1168" t="inlineStr">
         <is>
-          <t>143.00</t>
+          <t>93.00</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>454.00</t>
+          <t>452.00</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
@@ -27144,7 +27144,7 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>147.00</t>
+          <t>137.00</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>397.00</t>
+          <t>394.00</t>
         </is>
       </c>
       <c r="C1252" t="inlineStr">
@@ -28002,7 +28002,7 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>400.00</t>
+          <t>358.00</t>
         </is>
       </c>
       <c r="C1254" t="inlineStr">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>734.00</t>
+          <t>698.00</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>4442.00</t>
+          <t>4432.00</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="B1355" t="inlineStr">
         <is>
-          <t>153.00</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="C1355" t="inlineStr">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>74.00</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
@@ -33898,7 +33898,7 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1353.00</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
@@ -33942,7 +33942,7 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>361.00</t>
+          <t>301.00</t>
         </is>
       </c>
       <c r="C1524" t="inlineStr">
@@ -34338,7 +34338,7 @@
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
@@ -34839,12 +34839,12 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>Gate Lock 12B PMHS</t>
+          <t>Gate Lock 12B ATC</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>14.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C1565" t="inlineStr">
@@ -34932,7 +34932,7 @@
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="B1601" t="inlineStr">
         <is>
-          <t>89.00</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="C1601" t="inlineStr">
@@ -36076,7 +36076,7 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>281.00</t>
+          <t>279.00</t>
         </is>
       </c>
       <c r="C1621" t="inlineStr">
@@ -36208,7 +36208,7 @@
       </c>
       <c r="B1627" t="inlineStr">
         <is>
-          <t>64.00</t>
+          <t>54.00</t>
         </is>
       </c>
       <c r="C1627" t="inlineStr">
@@ -36274,7 +36274,7 @@
       </c>
       <c r="B1630" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="C1630" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>11636.00</t>
+          <t>11476.00</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
@@ -36626,7 +36626,7 @@
       </c>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>1059.00</t>
+          <t>909.00</t>
         </is>
       </c>
       <c r="C1646" t="inlineStr">
@@ -36648,7 +36648,7 @@
       </c>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>12850.00</t>
+          <t>12774.00</t>
         </is>
       </c>
       <c r="C1647" t="inlineStr">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>4630.00</t>
+          <t>4580.00</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="B1677" t="inlineStr">
         <is>
-          <t>1660.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="C1677" t="inlineStr">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="B1690" t="inlineStr">
         <is>
-          <t>727.00</t>
+          <t>604.00</t>
         </is>
       </c>
       <c r="C1690" t="inlineStr">
@@ -37968,7 +37968,7 @@
       </c>
       <c r="B1707" t="inlineStr">
         <is>
-          <t>109.00</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="C1707" t="inlineStr">
@@ -38122,7 +38122,7 @@
       </c>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>295.25</t>
+          <t>294.25</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
@@ -38716,7 +38716,7 @@
       </c>
       <c r="B1741" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="C1741" t="inlineStr">
@@ -38738,7 +38738,7 @@
       </c>
       <c r="B1742" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="C1742" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="B1745" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C1745" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="B1746" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>66.00</t>
         </is>
       </c>
       <c r="C1746" t="inlineStr">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="B1853" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="C1853" t="inlineStr">
@@ -41290,7 +41290,7 @@
       </c>
       <c r="B1858" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="C1858" t="inlineStr">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="B1917" t="inlineStr">
         <is>
-          <t>2663.00</t>
+          <t>2613.00</t>
         </is>
       </c>
       <c r="C1917" t="inlineStr">
@@ -42610,7 +42610,7 @@
       </c>
       <c r="B1918" t="inlineStr">
         <is>
-          <t>3266.00</t>
+          <t>3166.00</t>
         </is>
       </c>
       <c r="C1918" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="B1932" t="inlineStr">
         <is>
-          <t>1264.00</t>
+          <t>1104.00</t>
         </is>
       </c>
       <c r="C1932" t="inlineStr">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="B1937" t="inlineStr">
         <is>
-          <t>4039.00</t>
+          <t>3839.00</t>
         </is>
       </c>
       <c r="C1937" t="inlineStr">
@@ -43138,7 +43138,7 @@
       </c>
       <c r="B1942" t="inlineStr">
         <is>
-          <t>1085.00</t>
+          <t>1061.00</t>
         </is>
       </c>
       <c r="C1942" t="inlineStr">
@@ -43226,7 +43226,7 @@
       </c>
       <c r="B1946" t="inlineStr">
         <is>
-          <t>245.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="C1946" t="inlineStr">
@@ -43270,7 +43270,7 @@
       </c>
       <c r="B1948" t="inlineStr">
         <is>
-          <t>1063.00</t>
+          <t>913.00</t>
         </is>
       </c>
       <c r="C1948" t="inlineStr">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="B1949" t="inlineStr">
         <is>
-          <t>247.00</t>
+          <t>187.00</t>
         </is>
       </c>
       <c r="C1949" t="inlineStr">
@@ -43380,7 +43380,7 @@
       </c>
       <c r="B1953" t="inlineStr">
         <is>
-          <t>469.00</t>
+          <t>419.00</t>
         </is>
       </c>
       <c r="C1953" t="inlineStr">
@@ -43534,7 +43534,7 @@
       </c>
       <c r="B1960" t="inlineStr">
         <is>
-          <t>27.00</t>
+          <t>17.00</t>
         </is>
       </c>
       <c r="C1960" t="inlineStr">
@@ -44150,7 +44150,7 @@
       </c>
       <c r="B1988" t="inlineStr">
         <is>
-          <t>354.00</t>
+          <t>314.00</t>
         </is>
       </c>
       <c r="C1988" t="inlineStr">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="B1989" t="inlineStr">
         <is>
-          <t>646.00</t>
+          <t>606.00</t>
         </is>
       </c>
       <c r="C1989" t="inlineStr">
@@ -44194,7 +44194,7 @@
       </c>
       <c r="B1990" t="inlineStr">
         <is>
-          <t>268.00</t>
+          <t>248.00</t>
         </is>
       </c>
       <c r="C1990" t="inlineStr">
@@ -44524,7 +44524,7 @@
       </c>
       <c r="B2005" t="inlineStr">
         <is>
-          <t>122.00</t>
+          <t>87.00</t>
         </is>
       </c>
       <c r="C2005" t="inlineStr">
@@ -45426,7 +45426,7 @@
       </c>
       <c r="B2046" t="inlineStr">
         <is>
-          <t>1049.00</t>
+          <t>1037.00</t>
         </is>
       </c>
       <c r="C2046" t="inlineStr">
@@ -45580,7 +45580,7 @@
       </c>
       <c r="B2053" t="inlineStr">
         <is>
-          <t>143.00</t>
+          <t>142.00</t>
         </is>
       </c>
       <c r="C2053" t="inlineStr">
@@ -45690,7 +45690,7 @@
       </c>
       <c r="B2058" t="inlineStr">
         <is>
-          <t>223.00</t>
+          <t>221.00</t>
         </is>
       </c>
       <c r="C2058" t="inlineStr">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>323.00</t>
+          <t>283.00</t>
         </is>
       </c>
       <c r="C2063" t="inlineStr">
@@ -45932,7 +45932,7 @@
       </c>
       <c r="B2069" t="inlineStr">
         <is>
-          <t>128.00</t>
+          <t>122.00</t>
         </is>
       </c>
       <c r="C2069" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B2081" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="C2081" t="inlineStr">
@@ -46944,7 +46944,7 @@
       </c>
       <c r="B2115" t="inlineStr">
         <is>
-          <t>107.00</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="C2115" t="inlineStr">
@@ -46966,7 +46966,7 @@
       </c>
       <c r="B2116" t="inlineStr">
         <is>
-          <t>278.00</t>
+          <t>276.00</t>
         </is>
       </c>
       <c r="C2116" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="B2122" t="inlineStr">
         <is>
-          <t>306.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="C2122" t="inlineStr">
@@ -47164,7 +47164,7 @@
       </c>
       <c r="B2125" t="inlineStr">
         <is>
-          <t>774.00</t>
+          <t>764.00</t>
         </is>
       </c>
       <c r="C2125" t="inlineStr">
@@ -47186,7 +47186,7 @@
       </c>
       <c r="B2126" t="inlineStr">
         <is>
-          <t>141.00</t>
+          <t>131.00</t>
         </is>
       </c>
       <c r="C2126" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>2486.00</t>
+          <t>2480.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="B2132" t="inlineStr">
         <is>
-          <t>889.00</t>
+          <t>876.00</t>
         </is>
       </c>
       <c r="C2132" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="B2133" t="inlineStr">
         <is>
-          <t>2070.00</t>
+          <t>2047.00</t>
         </is>
       </c>
       <c r="C2133" t="inlineStr">
@@ -47626,7 +47626,7 @@
       </c>
       <c r="B2146" t="inlineStr">
         <is>
-          <t>1830.00</t>
+          <t>1829.00</t>
         </is>
       </c>
       <c r="C2146" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Drawer Lock 3/4" Iron GVI (Dozen)</t>
+          <t>Drawer Lock 3/4" Iron GVI (درجن)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Drawer Lock 3/4" Silo (Dozen)</t>
+          <t>Drawer Lock 3/4" Silo (درجن)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thumb Handle KE27L MAB</t>
+          <t>Thumb Lock KE27L MAB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>201.00</t>
+          <t>172.00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3423,7 +3423,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Hinges 2" Sitara Zinc (Box)</t>
+          <t>Hinges 2" Sitara Zinc (پڑی)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Double Bracket CP 21# Iron Hvy (BOX)</t>
+          <t>Double Bracket CP 21# Iron Hvy (درجن)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4941,7 +4941,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Hinges 5" Sitara Zinc (Box)</t>
+          <t>Hinges 5" Sitara Zinc (درجن)</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>22.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>29.00</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -14841,7 +14841,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Double Bracket Reg 21# CP (BOX)</t>
+          <t>Double Bracket Reg 21# CP (درجن)</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -15589,7 +15589,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>602# 8" AB Tower Bolt (Box)</t>
+          <t>602# 8" AB Tower Bolt (درجن)</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -15677,7 +15677,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>602# 8" AC Tower Bolt (Box)</t>
+          <t>602# 8" AC Tower Bolt (درجن)</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -15721,7 +15721,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>602# 4" AC Tower Bolt (Box)</t>
+          <t>602# 4" AC Tower Bolt (درجن)</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -17789,7 +17789,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>Hinges Imran 3" Zinc (Box)</t>
+          <t>Hinges Imran 3" Zinc (پڑی)</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -17811,7 +17811,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Hinges 3" Sitara Zinc (Box)</t>
+          <t>Hinges 3" Sitara Zinc (پڑی)</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>1531.00</t>
+          <t>1516.00</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
@@ -23069,12 +23069,12 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>Bracket 21# Single (Doz.)</t>
+          <t>Bracket 21# سنگل (درجن)</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>377.00</t>
+          <t>371.00</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="B1350" t="inlineStr">
         <is>
-          <t>358.00</t>
+          <t>355.00</t>
         </is>
       </c>
       <c r="C1350" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="B1604" t="inlineStr">
         <is>
-          <t>208.00</t>
+          <t>203.00</t>
         </is>
       </c>
       <c r="C1604" t="inlineStr">
@@ -35768,7 +35768,7 @@
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>294.00</t>
+          <t>289.00</t>
         </is>
       </c>
       <c r="C1607" t="inlineStr">
@@ -35812,7 +35812,7 @@
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="C1609" t="inlineStr">
@@ -40498,12 +40498,12 @@
       </c>
       <c r="B1822" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="C1822" t="inlineStr">
         <is>
-          <t>57.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="D1822" t="inlineStr">
@@ -40564,7 +40564,7 @@
       </c>
       <c r="B1825" t="inlineStr">
         <is>
-          <t>139.00</t>
+          <t>579.00</t>
         </is>
       </c>
       <c r="C1825" t="inlineStr">
@@ -40586,7 +40586,7 @@
       </c>
       <c r="B1826" t="inlineStr">
         <is>
-          <t>192.00</t>
+          <t>672.00</t>
         </is>
       </c>
       <c r="C1826" t="inlineStr">
@@ -40608,7 +40608,7 @@
       </c>
       <c r="B1827" t="inlineStr">
         <is>
-          <t>194.00</t>
+          <t>264.00</t>
         </is>
       </c>
       <c r="C1827" t="inlineStr">
@@ -42764,7 +42764,7 @@
       </c>
       <c r="B1925" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>94.00</t>
         </is>
       </c>
       <c r="C1925" t="inlineStr">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>283.00</t>
+          <t>273.00</t>
         </is>
       </c>
       <c r="C2063" t="inlineStr">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="B2066" t="inlineStr">
         <is>
-          <t>282.00</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="C2066" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="B2081" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="C2081" t="inlineStr">
@@ -46724,7 +46724,7 @@
       </c>
       <c r="B2105" t="inlineStr">
         <is>
-          <t>1097.00</t>
+          <t>1082.00</t>
         </is>
       </c>
       <c r="C2105" t="inlineStr">
@@ -46768,7 +46768,7 @@
       </c>
       <c r="B2107" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>318.00</t>
         </is>
       </c>
       <c r="C2107" t="inlineStr">

--- a/salesman_prices.xlsx
+++ b/salesman_prices.xlsx
@@ -1289,7 +1289,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hinges 4" Pistol Zinc (Doz.)</t>
+          <t>Hinges 4" Pistol Zinc (درجن)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>36.00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>302.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>714.00</t>
+          <t>679.00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5579,12 +5579,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Bracket Single GT Awan 16# (Dozen)</t>
+          <t>Bracket Single GT Awan 16# (درجن)</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>144.00</t>
+          <t>129.00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>117.00</t>
+          <t>116.00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>53.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>1950.00</t>
+          <t>1850.00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Drawer Lock ¾" Full Diecast PK (Dozen)</t>
+          <t>Drawer Lock ¾" Full Diecast PK (درجن)</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>173.00</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -14049,7 +14049,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Roshan dan catcher (Doz)</t>
+          <t>Roshan dan catcher (درجن)</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -14846,7 +14846,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>64.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>344.26</t>
+          <t>330.46</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>59.00</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -18141,7 +18141,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>Tower Bolt 3" AB (Dozen)</t>
+          <t>Tower Bolt 3" AB (درجن)</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>4762.00</t>
+          <t>4682.00</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>29.00</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -19285,7 +19285,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>Drawer Lock Full Diecast 3/4" MK (Dozen)</t>
+          <t>Drawer Lock Full Diecast 3/4" MK (درجن)</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -19312,7 +19312,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>787.00</t>
+          <t>786.00</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>329.00</t>
+          <t>327.00</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>74.00</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>125.00</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>579.00</t>
+          <t>571.00</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>9621.00</t>
+          <t>9619.00</t>
         </is>
       </c>
       <c r="C1023" t="inlineStr">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>371.00</t>
+          <t>359.00</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>3108.00</t>
+          <t>3008.00</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>240.00</t>
+          <t>234.00</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>934.00</t>
+          <t>904.00</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="B1166" t="inlineStr">
         <is>
-          <t>250.00</t>
+          <t>249.00</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="B1169" t="inlineStr">
         <is>
-          <t>321.00</t>
+          <t>306.00</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="B1192" t="inlineStr">
         <is>
-          <t>870.00</t>
+          <t>670.00</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>615.00</t>
+          <t>603.00</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr">
@@ -31258,7 +31258,7 @@
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>137.00</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
@@ -33898,7 +33898,7 @@
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>1353.00</t>
+          <t>1347.00</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
@@ -34184,7 +34184,7 @@
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>506.00</t>
+          <t>502.00</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
@@ -35768,7 +35768,7 @@
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>289.00</t>
+          <t>279.00</t>
         </is>
       </c>
       <c r="C1607" t="inlineStr">
@@ -35812,7 +35812,7 @@
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="C1609" t="inlineStr">
@@ -36076,7 +36076,7 @@
       </c>
       <c r="B1621" t="inlineStr">
         <is>
-          <t>279.00</t>
+          <t>266.00</t>
         </is>
       </c>
       <c r="C1621" t="inlineStr">
@@ -36494,7 +36494,7 @@
       </c>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>7068.00</t>
+          <t>7028.00</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="B1644" t="inlineStr">
         <is>
-          <t>11476.00</t>
+          <t>11436.00</t>
         </is>
       </c>
       <c r="C1644" t="inlineStr">
@@ -36648,7 +36648,7 @@
       </c>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>12774.00</t>
+          <t>12730.00</t>
         </is>
       </c>
       <c r="C1647" t="inlineStr">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>4580.00</t>
+          <t>4510.00</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="B1704" t="inlineStr">
         <is>
-          <t>180.00</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="C1704" t="inlineStr">
@@ -38034,7 +38034,7 @@
       </c>
       <c r="B1710" t="inlineStr">
         <is>
-          <t>53.75</t>
+          <t>52.75</t>
         </is>
       </c>
       <c r="C1710" t="inlineStr">
@@ -38078,7 +38078,7 @@
       </c>
       <c r="B1712" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>271.00</t>
         </is>
       </c>
       <c r="C1712" t="inlineStr">
@@ -38122,7 +38122,7 @@
       </c>
       <c r="B1714" t="inlineStr">
         <is>
-          <t>294.25</t>
+          <t>292.25</t>
         </is>
       </c>
       <c r="C1714" t="inlineStr">
@@ -38980,7 +38980,7 @@
       </c>
       <c r="B1753" t="inlineStr">
         <is>
-          <t>68.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="C1753" t="inlineStr">
@@ -39024,7 +39024,7 @@
       </c>
       <c r="B1755" t="inlineStr">
         <is>
-          <t>91.00</t>
+          <t>79.00</t>
         </is>
       </c>
       <c r="C1755" t="inlineStr">
@@ -39046,7 +39046,7 @@
       </c>
       <c r="B1756" t="inlineStr">
         <is>
-          <t>300.00</t>
+          <t>288.00</t>
         </is>
       </c>
       <c r="C1756" t="inlineStr">
@@ -39129,7 +39129,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>Hanlde 085-Reg AC (Doz)</t>
+          <t>Hanlde 085-Reg AC (درجن)</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -40718,7 +40718,7 @@
       </c>
       <c r="B1832" t="inlineStr">
         <is>
-          <t>232.00</t>
+          <t>230.00</t>
         </is>
       </c>
       <c r="C1832" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="B1915" t="inlineStr">
         <is>
-          <t>675.00</t>
+          <t>653.00</t>
         </is>
       </c>
       <c r="C1915" t="inlineStr">
@@ -43204,7 +43204,7 @@
       </c>
       <c r="B1945" t="inlineStr">
         <is>
-          <t>254.00</t>
+          <t>248.00</t>
         </is>
       </c>
       <c r="C1945" t="inlineStr">
@@ -45712,7 +45712,7 @@
       </c>
       <c r="B2059" t="inlineStr">
         <is>
-          <t>176.00</t>
+          <t>172.00</t>
         </is>
       </c>
       <c r="C2059" t="inlineStr">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="B2066" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>222.00</t>
         </is>
       </c>
       <c r="C2066" t="inlineStr">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="B2067" t="inlineStr">
         <is>
-          <t>303.00</t>
+          <t>253.00</t>
         </is>
       </c>
       <c r="C2067" t="inlineStr">
@@ -46482,7 +46482,7 @@
       </c>
       <c r="B2094" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>70.00</t>
         </is>
       </c>
       <c r="C2094" t="inlineStr">
@@ -46548,7 +46548,7 @@
       </c>
       <c r="B2097" t="inlineStr">
         <is>
-          <t>138.00</t>
+          <t>130.00</t>
         </is>
       </c>
       <c r="C2097" t="inlineStr">
@@ -46878,7 +46878,7 @@
       </c>
       <c r="B2112" t="inlineStr">
         <is>
-          <t>2436.00</t>
+          <t>2428.00</t>
         </is>
       </c>
       <c r="C2112" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="B2127" t="inlineStr">
         <is>
-          <t>2480.00</t>
+          <t>2473.00</t>
         </is>
       </c>
       <c r="C2127" t="inlineStr">
@@ -47296,7 +47296,7 @@
       </c>
       <c r="B2131" t="inlineStr">
         <is>
-          <t>558.00</t>
+          <t>551.00</t>
         </is>
       </c>
       <c r="C2131" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="B2132" t="inlineStr">
         <is>
-          <t>876.00</t>
+          <t>863.00</t>
         </is>
       </c>
       <c r="C2132" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="B2133" t="inlineStr">
         <is>
-          <t>2047.00</t>
+          <t>2040.00</t>
         </is>
       </c>
       <c r="C2133" t="inlineStr">
@@ -47428,7 +47428,7 @@
       </c>
       <c r="B2137" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>66.00</t>
         </is>
       </c>
       <c r="C2137" t="inlineStr">
@@ -47626,7 +47626,7 @@
       </c>
       <c r="B2146" t="inlineStr">
         <is>
-          <t>1829.00</t>
+          <t>1805.00</t>
         </is>
       </c>
       <c r="C2146" t="inlineStr">
